--- a/research/traditional_assets/database/data/indonesia/indonesia_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/indonesia/indonesia_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ25"/>
+  <dimension ref="A1:AQ20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0684</v>
+        <v>0.129</v>
       </c>
       <c r="E2">
-        <v>0.078</v>
+        <v>0.161</v>
       </c>
       <c r="F2">
-        <v>0.273</v>
+        <v>0.2475</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,91 +603,91 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>-0.0002205793400608881</v>
+        <v>-0.0002036751178265999</v>
       </c>
       <c r="J2">
-        <v>-0.0001754062325019014</v>
+        <v>-0.0001696105769869465</v>
       </c>
       <c r="K2">
-        <v>6274.383</v>
+        <v>9417.780000000001</v>
       </c>
       <c r="L2">
-        <v>0.3197123172428764</v>
+        <v>0.3828471681331029</v>
       </c>
       <c r="M2">
-        <v>2761.653</v>
+        <v>4477.2</v>
       </c>
       <c r="N2">
-        <v>0.01600639988686308</v>
+        <v>0.02675966684896137</v>
       </c>
       <c r="O2">
-        <v>0.4401473419776893</v>
+        <v>0.4753986608308964</v>
       </c>
       <c r="P2">
-        <v>2756.827</v>
+        <v>4395.9</v>
       </c>
       <c r="Q2">
-        <v>0.01597842863708839</v>
+        <v>0.02627374687334702</v>
       </c>
       <c r="R2">
-        <v>0.4393781826834606</v>
+        <v>0.4667660531462828</v>
       </c>
       <c r="S2">
-        <v>4.826</v>
+        <v>81.29999999999995</v>
       </c>
       <c r="T2">
-        <v>0.001747504121625708</v>
+        <v>0.01815867059769498</v>
       </c>
       <c r="U2">
-        <v>26060.77</v>
+        <v>16558</v>
       </c>
       <c r="V2">
-        <v>0.1510468932844078</v>
+        <v>0.09896510401257534</v>
       </c>
       <c r="W2">
-        <v>0.07640803465931469</v>
+        <v>0.0878651706282072</v>
       </c>
       <c r="X2">
-        <v>0.05184647792073496</v>
+        <v>0.08523105886317225</v>
       </c>
       <c r="Y2">
-        <v>0.02456155673857973</v>
+        <v>0.002634111765034947</v>
       </c>
       <c r="Z2">
-        <v>0.3836018950360627</v>
+        <v>0.4083747943426618</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.04986720277382792</v>
+        <v>0.08307327416953508</v>
       </c>
       <c r="AC2">
-        <v>-0.04986546819530807</v>
+        <v>-0.08307327416953508</v>
       </c>
       <c r="AD2">
-        <v>24489.405</v>
+        <v>30013.769</v>
       </c>
       <c r="AE2">
-        <v>34.46944700417767</v>
+        <v>27.61134699727118</v>
       </c>
       <c r="AF2">
-        <v>24523.87444700418</v>
+        <v>30041.38034699727</v>
       </c>
       <c r="AG2">
-        <v>-1536.895552995822</v>
+        <v>13483.38034699727</v>
       </c>
       <c r="AH2">
-        <v>0.1244499220386288</v>
+        <v>0.1522216462925536</v>
       </c>
       <c r="AI2">
-        <v>0.2786652724366935</v>
+        <v>0.3220159872440643</v>
       </c>
       <c r="AJ2">
-        <v>-0.008987829715696881</v>
+        <v>0.07457833054298217</v>
       </c>
       <c r="AK2">
-        <v>-0.0248110461491185</v>
+        <v>0.1757168150635487</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -696,10 +696,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>9547.526315789473</v>
+        <v>58620.642578125</v>
       </c>
       <c r="AP2">
-        <v>-599.179552824882</v>
+        <v>26334.72724022905</v>
       </c>
     </row>
     <row r="3">
@@ -719,7 +719,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.459</v>
+        <v>0.436</v>
+      </c>
+      <c r="E3">
+        <v>0.97</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,16 +731,16 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.01359399659162135</v>
+        <v>0.004482254146764264</v>
       </c>
       <c r="J3">
-        <v>0.01189189113603179</v>
+        <v>0.003522983846415093</v>
       </c>
       <c r="K3">
-        <v>5.2</v>
+        <v>20.7</v>
       </c>
       <c r="L3">
-        <v>0.4684684684684685</v>
+        <v>0.4859154929577464</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -761,55 +764,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>10.3</v>
+        <v>22.2</v>
       </c>
       <c r="V3">
-        <v>0.001798152965206613</v>
+        <v>0.009044243461256417</v>
       </c>
       <c r="W3">
-        <v>0.2222222222222222</v>
+        <v>0.2297447280799112</v>
       </c>
       <c r="X3">
-        <v>0.05079399364874768</v>
+        <v>0.07962605675209722</v>
       </c>
       <c r="Y3">
-        <v>0.1714282285734746</v>
+        <v>0.150118671327814</v>
       </c>
       <c r="Z3">
-        <v>1.417166034528264</v>
+        <v>0.1351543082054109</v>
       </c>
       <c r="AA3">
-        <v>0.01685278420429198</v>
+        <v>0.0004761464445810694</v>
       </c>
       <c r="AB3">
-        <v>0.05077632395727288</v>
+        <v>0.07971087659065892</v>
       </c>
       <c r="AC3">
-        <v>-0.0339235397529809</v>
+        <v>-0.07923473014607786</v>
       </c>
       <c r="AD3">
-        <v>235.2</v>
+        <v>2.72</v>
       </c>
       <c r="AE3">
-        <v>0.420533189165015</v>
+        <v>0.1952798667392118</v>
       </c>
       <c r="AF3">
-        <v>235.620533189165</v>
+        <v>2.915279866739212</v>
       </c>
       <c r="AG3">
-        <v>225.320533189165</v>
+        <v>-19.28472013326079</v>
       </c>
       <c r="AH3">
-        <v>0.03950898300446757</v>
+        <v>0.001186271308513408</v>
       </c>
       <c r="AI3">
-        <v>0.7233824987395755</v>
+        <v>0.006980778738913662</v>
       </c>
       <c r="AJ3">
-        <v>0.03784723957144413</v>
+        <v>-0.007918777618935668</v>
       </c>
       <c r="AK3">
-        <v>0.7143496046721697</v>
+        <v>-0.04877080152228822</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -818,10 +821,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>1000.851063829787</v>
+        <v>11.82608695652174</v>
       </c>
       <c r="AP3">
-        <v>958.8107795283618</v>
+        <v>-83.8466092750469</v>
       </c>
     </row>
     <row r="4">
@@ -832,7 +835,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PT Bank Pembangunan Daerah Jawa Barat dan Banten Tbk (IDX:BJBR)</t>
+          <t>PT Bank Bisnis Internasional, Tbk (IDX:BBSI)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -841,10 +844,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.06519999999999999</v>
+        <v>0.23</v>
       </c>
       <c r="E4">
-        <v>0.0257</v>
+        <v>0.315</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -859,85 +862,82 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>133.4</v>
+        <v>5.2</v>
       </c>
       <c r="L4">
-        <v>0.2202774108322325</v>
+        <v>0.6088992974238877</v>
       </c>
       <c r="M4">
-        <v>65.90000000000001</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.07167718077006745</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>0.4940029985007496</v>
+        <v>-0</v>
       </c>
       <c r="P4">
-        <v>65.90000000000001</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.07167718077006745</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.4940029985007496</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>1131.5</v>
+        <v>20.5</v>
       </c>
       <c r="V4">
-        <v>1.230693930824451</v>
+        <v>0.03064733143967708</v>
       </c>
       <c r="W4">
-        <v>0.1784615384615385</v>
+        <v>0.06961178045515395</v>
       </c>
       <c r="X4">
-        <v>0.08152573426992915</v>
+        <v>0.07959068789865785</v>
       </c>
       <c r="Y4">
-        <v>0.09693580419160933</v>
+        <v>-0.009978907443503895</v>
       </c>
       <c r="Z4">
-        <v>1.099491648511256</v>
+        <v>0.1721149582812689</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.04895139466917051</v>
+        <v>0.07958904586124638</v>
       </c>
       <c r="AC4">
-        <v>-0.04895139466917051</v>
+        <v>-0.07958904586124638</v>
       </c>
       <c r="AD4">
-        <v>1288.2</v>
+        <v>0.112</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>1288.2</v>
+        <v>0.112</v>
       </c>
       <c r="AG4">
-        <v>156.7</v>
+        <v>-20.388</v>
       </c>
       <c r="AH4">
-        <v>0.583529624932053</v>
+        <v>0.0001674110479333704</v>
       </c>
       <c r="AI4">
-        <v>0.5975230762094716</v>
+        <v>0.0007982211072467075</v>
       </c>
       <c r="AJ4">
-        <v>0.1456184369482391</v>
+        <v>-0.03143812296457121</v>
       </c>
       <c r="AK4">
-        <v>0.1529675907848497</v>
+        <v>-0.1701665943311188</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -954,7 +954,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>P.T. Bank Pan Indonesia Tbk (IDX:PNBN)</t>
+          <t>PT Bank Jago Tbk (IDX:ARTO)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.034</v>
-      </c>
-      <c r="E5">
-        <v>0.09140000000000001</v>
+        <v>1.916</v>
+      </c>
+      <c r="F5">
+        <v>2.26</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -981,10 +981,10 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>213.4</v>
+        <v>10.5</v>
       </c>
       <c r="L5">
-        <v>0.3365399779214635</v>
+        <v>0.1586102719033232</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -1008,55 +1008,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>664.5</v>
+        <v>38.8</v>
       </c>
       <c r="V5">
-        <v>0.5172011207970112</v>
+        <v>0.01176149625632786</v>
       </c>
       <c r="W5">
-        <v>0.07640803465931469</v>
+        <v>0.01844370279290357</v>
       </c>
       <c r="X5">
-        <v>0.06449585206028258</v>
+        <v>0.07962670788927217</v>
       </c>
       <c r="Y5">
-        <v>0.01191218259903211</v>
+        <v>-0.06118300509636861</v>
       </c>
       <c r="Z5">
-        <v>0.1791293539365519</v>
+        <v>0.1629137443090931</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.04924950383476263</v>
+        <v>0.07961095307521798</v>
       </c>
       <c r="AC5">
-        <v>-0.04924950383476263</v>
+        <v>-0.07961095307521798</v>
       </c>
       <c r="AD5">
-        <v>831.9</v>
+        <v>3.98</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>831.9</v>
+        <v>3.98</v>
       </c>
       <c r="AG5">
-        <v>167.4</v>
+        <v>-34.82</v>
       </c>
       <c r="AH5">
-        <v>0.3930174327963339</v>
+        <v>0.001205008961875696</v>
       </c>
       <c r="AI5">
-        <v>0.1980761446701112</v>
+        <v>0.007259064711461298</v>
       </c>
       <c r="AJ5">
-        <v>0.1152733783225451</v>
+        <v>-0.01066763069532609</v>
       </c>
       <c r="AK5">
-        <v>0.04734966340442382</v>
+        <v>-0.06834419408023867</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PT Bank OCBC NISP Tbk (IDX:NISP)</t>
+          <t>PT Bank Aladin Syariah Tbk (IDX:BANK)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1081,12 +1081,6 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D6">
-        <v>0.0452</v>
-      </c>
-      <c r="E6">
-        <v>0.0401</v>
-      </c>
       <c r="G6">
         <v>0</v>
       </c>
@@ -1100,10 +1094,10 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>153.3</v>
+        <v>-13.6</v>
       </c>
       <c r="L6">
-        <v>0.3174570304410851</v>
+        <v>-3.908045977011494</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1112,7 +1106,7 @@
         <v>-0</v>
       </c>
       <c r="O6">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P6">
         <v>-0</v>
@@ -1121,61 +1115,61 @@
         <v>-0</v>
       </c>
       <c r="R6">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
       <c r="U6">
-        <v>252.1</v>
+        <v>31.8</v>
       </c>
       <c r="V6">
-        <v>0.2342719078152588</v>
+        <v>0.02549915804666827</v>
       </c>
       <c r="W6">
-        <v>0.07713207547169812</v>
+        <v>-0.1763942931258106</v>
       </c>
       <c r="X6">
-        <v>0.05934759240693222</v>
+        <v>0.0796257466351912</v>
       </c>
       <c r="Y6">
-        <v>0.0177844830647659</v>
+        <v>-0.2560200397610018</v>
       </c>
       <c r="Z6">
-        <v>0.2309642242203941</v>
+        <v>0.04620286776420606</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.04940192826001656</v>
+        <v>0.0796141574493949</v>
       </c>
       <c r="AC6">
-        <v>-0.04940192826001656</v>
+        <v>-0.0796141574493949</v>
       </c>
       <c r="AD6">
-        <v>451.6</v>
+        <v>1.47</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>451.6</v>
+        <v>1.47</v>
       </c>
       <c r="AG6">
-        <v>199.5</v>
+        <v>-30.33</v>
       </c>
       <c r="AH6">
-        <v>0.2956077763958893</v>
+        <v>0.001177346884836253</v>
       </c>
       <c r="AI6">
-        <v>0.1685703620754013</v>
+        <v>0.01098080227085979</v>
       </c>
       <c r="AJ6">
-        <v>0.1563969896519285</v>
+        <v>-0.02492665006533692</v>
       </c>
       <c r="AK6">
-        <v>0.08220363426593598</v>
+        <v>-0.2971490153816009</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1192,7 +1186,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PT Bank BTPN Tbk (IDX:BTPN)</t>
+          <t>PT Bank Central Asia Tbk (IDX:BBCA)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1201,10 +1195,13 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0446</v>
+        <v>0.0824</v>
       </c>
       <c r="E7">
-        <v>0.0545</v>
+        <v>0.107</v>
+      </c>
+      <c r="F7">
+        <v>0.148</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1213,103 +1210,97 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>-0.006157776993817912</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>-0.004773293305026343</v>
+        <v>0</v>
       </c>
       <c r="K7">
-        <v>157.6</v>
+        <v>2441.5</v>
       </c>
       <c r="L7">
-        <v>0.2166323024054983</v>
+        <v>0.4759444812663262</v>
       </c>
       <c r="M7">
-        <v>7.286</v>
+        <v>1173.8</v>
       </c>
       <c r="N7">
-        <v>0.004930969139144559</v>
+        <v>0.01740094668977305</v>
       </c>
       <c r="O7">
-        <v>0.04623096446700507</v>
+        <v>0.4807700184312922</v>
       </c>
       <c r="P7">
-        <v>7.27</v>
+        <v>1173.8</v>
       </c>
       <c r="Q7">
-        <v>0.004920140768814293</v>
+        <v>0.01740094668977305</v>
       </c>
       <c r="R7">
-        <v>0.04612944162436548</v>
+        <v>0.4807700184312922</v>
       </c>
       <c r="S7">
-        <v>0.01600000000000001</v>
+        <v>0</v>
       </c>
       <c r="T7">
-        <v>0.002195992314026903</v>
+        <v>0</v>
       </c>
       <c r="U7">
-        <v>1200.8</v>
+        <v>3384.7</v>
       </c>
       <c r="V7">
-        <v>0.8126691932864104</v>
+        <v>0.05017633690652142</v>
       </c>
       <c r="W7">
-        <v>0.07570008165617945</v>
+        <v>0.1763083211172813</v>
       </c>
       <c r="X7">
-        <v>0.09490155409078589</v>
+        <v>0.07968787316317813</v>
       </c>
       <c r="Y7">
-        <v>-0.01920147243460645</v>
+        <v>0.09662044795410318</v>
       </c>
       <c r="Z7">
-        <v>0.1602797512400383</v>
+        <v>0.761900518350191</v>
       </c>
       <c r="AA7">
-        <v>-0.0007650622635253626</v>
+        <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.04882251271448662</v>
+        <v>0.0796295787975931</v>
       </c>
       <c r="AC7">
-        <v>-0.04958757497801199</v>
+        <v>-0.0796295787975931</v>
       </c>
       <c r="AD7">
-        <v>2910.9</v>
+        <v>200.4</v>
       </c>
       <c r="AE7">
-        <v>34.04891381501265</v>
+        <v>0</v>
       </c>
       <c r="AF7">
-        <v>2944.948913815013</v>
+        <v>200.4</v>
       </c>
       <c r="AG7">
-        <v>1744.148913815013</v>
+        <v>-3184.3</v>
       </c>
       <c r="AH7">
-        <v>0.6658940288067088</v>
+        <v>0.002962021387449839</v>
       </c>
       <c r="AI7">
-        <v>0.543805132442915</v>
+        <v>0.01418439716312057</v>
       </c>
       <c r="AJ7">
-        <v>0.5413671147171089</v>
+        <v>-0.04954427913952931</v>
       </c>
       <c r="AK7">
-        <v>0.4138301788549798</v>
+        <v>-0.2963931679620235</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
         <v>0</v>
-      </c>
-      <c r="AN7">
-        <v>1249.31330472103</v>
-      </c>
-      <c r="AP7">
-        <v>748.5617655858424</v>
       </c>
     </row>
     <row r="8">
@@ -1320,7 +1311,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PT Bank Pembangunan Daerah Jawa Timur Tbk (IDX:BJTM)</t>
+          <t>PT Bank Panin Dubai Syariah Tbk (IDX:PNBS)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1328,107 +1319,80 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D8">
-        <v>0.0549</v>
-      </c>
-      <c r="E8">
-        <v>0.0898</v>
-      </c>
-      <c r="F8">
-        <v>0.03</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
       <c r="K8">
-        <v>110.2</v>
-      </c>
-      <c r="L8">
-        <v>0.3794765840220386</v>
+        <v>-42.8</v>
       </c>
       <c r="M8">
-        <v>51.3</v>
+        <v>-0</v>
       </c>
       <c r="N8">
-        <v>0.06507674743118103</v>
+        <v>-0</v>
       </c>
       <c r="O8">
-        <v>0.4655172413793103</v>
+        <v>0</v>
       </c>
       <c r="P8">
-        <v>51.3</v>
+        <v>-0</v>
       </c>
       <c r="Q8">
-        <v>0.06507674743118103</v>
+        <v>-0</v>
       </c>
       <c r="R8">
-        <v>0.4655172413793103</v>
+        <v>0</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
       <c r="U8">
-        <v>989</v>
+        <v>66.3</v>
       </c>
       <c r="V8">
-        <v>1.254598503107954</v>
+        <v>0.4236421725239616</v>
       </c>
       <c r="W8">
-        <v>0.169904409497379</v>
+        <v>-0.1959706959706959</v>
       </c>
       <c r="X8">
-        <v>0.05263929722235655</v>
+        <v>0.07972753914207885</v>
       </c>
       <c r="Y8">
-        <v>0.1172651122750224</v>
+        <v>-0.2756982351127748</v>
       </c>
       <c r="Z8">
-        <v>20.02758620689655</v>
+        <v>0</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.04969335490453178</v>
+        <v>0.07968678191995188</v>
       </c>
       <c r="AC8">
-        <v>-0.04969335490453178</v>
+        <v>-0.07968678191995188</v>
       </c>
       <c r="AD8">
-        <v>96.8</v>
+        <v>0.644</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>96.8</v>
+        <v>0.644</v>
       </c>
       <c r="AG8">
-        <v>-892.2</v>
+        <v>-65.65599999999999</v>
       </c>
       <c r="AH8">
-        <v>0.1093661733137499</v>
+        <v>0.004098152013439902</v>
       </c>
       <c r="AI8">
-        <v>0.115831039846835</v>
+        <v>0.004119121936243157</v>
       </c>
       <c r="AJ8">
-        <v>8.587102983638106</v>
+        <v>-0.7227334771696533</v>
       </c>
       <c r="AK8">
-        <v>5.819960861056749</v>
+        <v>-0.7291546355115276</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1445,7 +1409,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PT Bank Central Asia Tbk (IDX:BBCA)</t>
+          <t>PT Bank Maspion Indonesia Tbk (IDX:BMAS)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1454,13 +1418,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.0684</v>
+        <v>0.09210000000000002</v>
       </c>
       <c r="E9">
-        <v>0.08900000000000001</v>
-      </c>
-      <c r="F9">
-        <v>0.161</v>
+        <v>0.116</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1475,85 +1436,82 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>2120.7</v>
+        <v>7.84</v>
       </c>
       <c r="L9">
-        <v>0.4533347584437794</v>
+        <v>0.2861313868613139</v>
       </c>
       <c r="M9">
-        <v>914.8</v>
+        <v>-0</v>
       </c>
       <c r="N9">
-        <v>0.01466881321796689</v>
+        <v>-0</v>
       </c>
       <c r="O9">
-        <v>0.4313670014617815</v>
+        <v>-0</v>
       </c>
       <c r="P9">
-        <v>914.8</v>
+        <v>-0</v>
       </c>
       <c r="Q9">
-        <v>0.01466881321796689</v>
+        <v>-0</v>
       </c>
       <c r="R9">
-        <v>0.4313670014617815</v>
+        <v>-0</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
       <c r="U9">
-        <v>7185.2</v>
+        <v>51.5</v>
       </c>
       <c r="V9">
-        <v>0.1152146444400259</v>
+        <v>0.1661290322580645</v>
       </c>
       <c r="W9">
-        <v>0.1761451887536858</v>
+        <v>0.08634361233480177</v>
       </c>
       <c r="X9">
-        <v>0.04991931087902302</v>
+        <v>0.07966797259519545</v>
       </c>
       <c r="Y9">
-        <v>0.1262258778746627</v>
+        <v>0.006675639739606318</v>
       </c>
       <c r="Z9">
-        <v>0.6040337783746094</v>
+        <v>3.30120481927711</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.04986070150659683</v>
+        <v>0.07983883487833272</v>
       </c>
       <c r="AC9">
-        <v>-0.04986070150659683</v>
+        <v>-0.07983883487833272</v>
       </c>
       <c r="AD9">
-        <v>151.3</v>
+        <v>0.743</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>151.3</v>
+        <v>0.743</v>
       </c>
       <c r="AG9">
-        <v>-7033.9</v>
+        <v>-50.757</v>
       </c>
       <c r="AH9">
-        <v>0.002420223018832311</v>
+        <v>0.002391043402425799</v>
       </c>
       <c r="AI9">
-        <v>0.01080066245966706</v>
+        <v>0.007951371424290744</v>
       </c>
       <c r="AJ9">
-        <v>-0.1271270221960358</v>
+        <v>-0.1957892787847695</v>
       </c>
       <c r="AK9">
-        <v>-1.030879939031539</v>
+        <v>-1.210142336027466</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1570,7 +1528,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PT Bank Aladin Syariah Tbk (IDX:BANK)</t>
+          <t>PT Bank Syariah Indonesia Tbk (IDX:BRIS)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1578,6 +1536,12 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
+      <c r="D10">
+        <v>0.6409999999999999</v>
+      </c>
+      <c r="E10">
+        <v>0.882</v>
+      </c>
       <c r="G10">
         <v>0</v>
       </c>
@@ -1591,82 +1555,85 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>-5.2</v>
+        <v>261.1</v>
       </c>
       <c r="L10">
-        <v>-0.7658321060382917</v>
+        <v>0.2617019144031272</v>
       </c>
       <c r="M10">
-        <v>-0</v>
+        <v>49.7</v>
       </c>
       <c r="N10">
-        <v>-0</v>
+        <v>0.01463658852632819</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>0.1903485254691689</v>
       </c>
       <c r="P10">
-        <v>-0</v>
+        <v>49.7</v>
       </c>
       <c r="Q10">
-        <v>-0</v>
+        <v>0.01463658852632819</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>0.1903485254691689</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
       <c r="U10">
-        <v>1.78</v>
+        <v>533.8</v>
       </c>
       <c r="V10">
-        <v>0.0008470140375921961</v>
+        <v>0.1572034397455531</v>
       </c>
       <c r="W10">
-        <v>-0.1181818181818182</v>
+        <v>0.1546251332464764</v>
       </c>
       <c r="X10">
-        <v>0.04986448861678964</v>
+        <v>0.08022603565671205</v>
       </c>
       <c r="Y10">
-        <v>-0.1680463067986078</v>
+        <v>0.07439909758976435</v>
       </c>
       <c r="Z10">
-        <v>0.1543743179337941</v>
+        <v>1.233403387316109</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.04986448861678964</v>
+        <v>0.07997773805004098</v>
       </c>
       <c r="AC10">
-        <v>-0.04986448861678964</v>
+        <v>-0.07997773805004098</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>62.8</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>62.8</v>
       </c>
       <c r="AG10">
-        <v>-1.78</v>
+        <v>-470.9999999999999</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>0.01815868609761739</v>
       </c>
       <c r="AI10">
-        <v>0</v>
+        <v>0.03355597114613946</v>
       </c>
       <c r="AJ10">
-        <v>-0.0008477320785628561</v>
+        <v>-0.1610476646378992</v>
       </c>
       <c r="AK10">
-        <v>-0.02363250132766862</v>
+        <v>-0.3520968827091275</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1683,7 +1650,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PT Bank Maspion Indonesia Tbk (IDX:BMAS)</t>
+          <t>PT Bank Mestika Dharma Tbk (IDX:BBMD)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1692,10 +1659,10 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.0454</v>
+        <v>0.0919</v>
       </c>
       <c r="E11">
-        <v>0.0204</v>
+        <v>0.139</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1710,28 +1677,28 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>5.24</v>
+        <v>36.9</v>
       </c>
       <c r="L11">
-        <v>0.2328888888888889</v>
+        <v>0.5</v>
       </c>
       <c r="M11">
-        <v>2.33</v>
+        <v>16.9</v>
       </c>
       <c r="N11">
-        <v>0.00433005017654711</v>
+        <v>0.03092972181551976</v>
       </c>
       <c r="O11">
-        <v>0.4446564885496183</v>
+        <v>0.4579945799457995</v>
       </c>
       <c r="P11">
-        <v>2.33</v>
+        <v>16.9</v>
       </c>
       <c r="Q11">
-        <v>0.00433005017654711</v>
+        <v>0.03092972181551976</v>
       </c>
       <c r="R11">
-        <v>0.4446564885496183</v>
+        <v>0.4579945799457995</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1740,55 +1707,55 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>82.5</v>
+        <v>53.9</v>
       </c>
       <c r="V11">
-        <v>0.1533172272811745</v>
+        <v>0.09864568081991215</v>
       </c>
       <c r="W11">
-        <v>0.06143024618991794</v>
+        <v>0.1319270647121916</v>
       </c>
       <c r="X11">
-        <v>0.04986448861678964</v>
+        <v>0.08339801606205824</v>
       </c>
       <c r="Y11">
-        <v>0.0115657575731283</v>
+        <v>0.04852904865013338</v>
       </c>
       <c r="Z11">
-        <v>0.4844961240310078</v>
+        <v>0.2691466083150985</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.04986448861678964</v>
+        <v>0.08204878885722168</v>
       </c>
       <c r="AC11">
-        <v>-0.04986448861678964</v>
+        <v>-0.08204878885722168</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>60.1</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>60.1</v>
       </c>
       <c r="AG11">
-        <v>-82.5</v>
+        <v>6.200000000000003</v>
       </c>
       <c r="AH11">
-        <v>0</v>
+        <v>0.09909315746084089</v>
       </c>
       <c r="AI11">
-        <v>0</v>
+        <v>0.1767127315495443</v>
       </c>
       <c r="AJ11">
-        <v>-0.1810798946444249</v>
+        <v>0.01121968874411872</v>
       </c>
       <c r="AK11">
-        <v>-9.939759036144581</v>
+        <v>0.02166317260656885</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1805,7 +1772,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PT Bank Amar Indonesia Tbk (IDX:AMAR)</t>
+          <t>P.T. Bank Pan Indonesia Tbk (IDX:PNBN)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1814,7 +1781,10 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.6840000000000001</v>
+        <v>-0.0139</v>
+      </c>
+      <c r="E12">
+        <v>-0.04480000000000001</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1829,28 +1799,28 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>-0.911</v>
+        <v>145.9</v>
       </c>
       <c r="L12">
-        <v>-0.04013215859030837</v>
+        <v>0.2822050290135397</v>
       </c>
       <c r="M12">
-        <v>0.427</v>
+        <v>31.6</v>
       </c>
       <c r="N12">
-        <v>0.00195692025664528</v>
+        <v>0.01331367179271119</v>
       </c>
       <c r="O12">
-        <v>-0.4687156970362239</v>
+        <v>0.2165867032213845</v>
       </c>
       <c r="P12">
-        <v>0.427</v>
+        <v>31.6</v>
       </c>
       <c r="Q12">
-        <v>0.00195692025664528</v>
+        <v>0.01331367179271119</v>
       </c>
       <c r="R12">
-        <v>-0.4687156970362239</v>
+        <v>0.2165867032213845</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -1859,55 +1829,55 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>6.65</v>
+        <v>615.7</v>
       </c>
       <c r="V12">
-        <v>0.03047662694775436</v>
+        <v>0.2594059405940594</v>
       </c>
       <c r="W12">
-        <v>-0.01267037552155772</v>
+        <v>0.04656729756471227</v>
       </c>
       <c r="X12">
-        <v>0.04986448861678964</v>
+        <v>0.08872234672350973</v>
       </c>
       <c r="Y12">
-        <v>-0.06253486413834736</v>
+        <v>-0.04215504915879746</v>
       </c>
       <c r="Z12">
-        <v>6.670584778136926</v>
+        <v>0.1566429328889562</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.04986448861678964</v>
+        <v>0.0840977594818485</v>
       </c>
       <c r="AC12">
-        <v>-0.04986448861678964</v>
+        <v>-0.0840977594818485</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>625.6</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>625.6</v>
       </c>
       <c r="AG12">
-        <v>-6.65</v>
+        <v>9.899999999999977</v>
       </c>
       <c r="AH12">
-        <v>0</v>
+        <v>0.2085959121069654</v>
       </c>
       <c r="AI12">
-        <v>0</v>
+        <v>0.1618168179819456</v>
       </c>
       <c r="AJ12">
-        <v>-0.03143464901914442</v>
+        <v>0.004153729965595358</v>
       </c>
       <c r="AK12">
-        <v>-0.09786607799852835</v>
+        <v>0.003045778981048479</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -1924,7 +1894,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PT Bank Bisnis Internasional, Tbk (IDX:BBSI)</t>
+          <t>PT Bank Rakyat Indonesia (Persero) Tbk (IDX:BBRI)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1933,10 +1903,13 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.253</v>
+        <v>0.141</v>
       </c>
       <c r="E13">
-        <v>0.426</v>
+        <v>0.14</v>
+      </c>
+      <c r="F13">
+        <v>0.226</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1951,82 +1924,85 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>4.15</v>
+        <v>3504.6</v>
       </c>
       <c r="L13">
-        <v>0.6023222060957911</v>
+        <v>0.41343919213845</v>
       </c>
       <c r="M13">
-        <v>-0</v>
+        <v>1815.4</v>
       </c>
       <c r="N13">
-        <v>-0</v>
+        <v>0.0379582739168071</v>
       </c>
       <c r="O13">
-        <v>-0</v>
+        <v>0.5180049078354163</v>
       </c>
       <c r="P13">
-        <v>-0</v>
+        <v>1734.1</v>
       </c>
       <c r="Q13">
-        <v>-0</v>
+        <v>0.03625836884385546</v>
       </c>
       <c r="R13">
-        <v>-0</v>
+        <v>0.4948068253152999</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>81.29999999999995</v>
+      </c>
+      <c r="T13">
+        <v>0.0447835187837391</v>
       </c>
       <c r="U13">
-        <v>25.1</v>
+        <v>4910.1</v>
       </c>
       <c r="V13">
-        <v>0.02546930492135972</v>
+        <v>0.1026654846088546</v>
       </c>
       <c r="W13">
-        <v>0.08718487394957984</v>
+        <v>0.1805471124620061</v>
       </c>
       <c r="X13">
-        <v>0.04986490134587823</v>
+        <v>0.08706410166428628</v>
       </c>
       <c r="Y13">
-        <v>0.03731997260370161</v>
+        <v>0.0934830107977198</v>
       </c>
       <c r="Z13">
-        <v>0.2053467648198373</v>
+        <v>0.414494369385889</v>
       </c>
       <c r="AA13">
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.04986455102984351</v>
+        <v>0.08431406207574342</v>
       </c>
       <c r="AC13">
-        <v>-0.04986455102984351</v>
+        <v>-0.08431406207574342</v>
       </c>
       <c r="AD13">
-        <v>0.018</v>
+        <v>10318.2</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>0.018</v>
+        <v>10318.2</v>
       </c>
       <c r="AG13">
-        <v>-25.082</v>
+        <v>5408.1</v>
       </c>
       <c r="AH13">
-        <v>1.826450658435462e-05</v>
+        <v>0.1774581902986359</v>
       </c>
       <c r="AI13">
-        <v>0.0002409058058299205</v>
+        <v>0.3434717335366118</v>
       </c>
       <c r="AJ13">
-        <v>-0.02611571211701572</v>
+        <v>0.1015905158891918</v>
       </c>
       <c r="AK13">
-        <v>-0.5055020355516143</v>
+        <v>0.2151980836264663</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2043,7 +2019,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PT Bank Jago Tbk (IDX:ARTO)</t>
+          <t>PT Bank Mega Tbk (IDX:MEGA)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2052,10 +2028,10 @@
         </is>
       </c>
       <c r="D14">
-        <v>0.5610000000000001</v>
-      </c>
-      <c r="F14">
-        <v>2.59</v>
+        <v>0.134</v>
+      </c>
+      <c r="E14">
+        <v>0.322</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2070,82 +2046,85 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>-8.15</v>
+        <v>270.5</v>
       </c>
       <c r="L14">
-        <v>-0.3687782805429864</v>
+        <v>0.4961482024944974</v>
       </c>
       <c r="M14">
-        <v>-0</v>
+        <v>183.9</v>
       </c>
       <c r="N14">
-        <v>-0</v>
+        <v>0.0463960441002094</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>0.6798521256931608</v>
       </c>
       <c r="P14">
-        <v>-0</v>
+        <v>183.9</v>
       </c>
       <c r="Q14">
-        <v>-0</v>
+        <v>0.0463960441002094</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>0.6798521256931608</v>
       </c>
       <c r="S14">
         <v>0</v>
       </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
       <c r="U14">
-        <v>167.4</v>
+        <v>149.8</v>
       </c>
       <c r="V14">
-        <v>0.01078677749855016</v>
+        <v>0.03779297121376492</v>
       </c>
       <c r="W14">
-        <v>-0.09963325183374083</v>
+        <v>0.2110972373965975</v>
       </c>
       <c r="X14">
-        <v>0.04987096817625379</v>
+        <v>0.08950215305168932</v>
       </c>
       <c r="Y14">
-        <v>-0.1495042200099946</v>
+        <v>0.1215950843449081</v>
       </c>
       <c r="Z14">
-        <v>0.3393213572854292</v>
+        <v>0.3396038370499564</v>
       </c>
       <c r="AA14">
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.04986546819530807</v>
+        <v>0.08511570165022238</v>
       </c>
       <c r="AC14">
-        <v>-0.04986546819530807</v>
+        <v>-0.08511570165022238</v>
       </c>
       <c r="AD14">
-        <v>4.45</v>
+        <v>1133.9</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>4.45</v>
+        <v>1133.9</v>
       </c>
       <c r="AG14">
-        <v>-162.95</v>
+        <v>984.1000000000001</v>
       </c>
       <c r="AH14">
-        <v>0.0002866630806940468</v>
+        <v>0.2224380100439423</v>
       </c>
       <c r="AI14">
-        <v>0.00775599128540305</v>
+        <v>0.487908777969019</v>
       </c>
       <c r="AJ14">
-        <v>-0.01061145281501428</v>
+        <v>0.1988964792433001</v>
       </c>
       <c r="AK14">
-        <v>-0.4010089824043314</v>
+        <v>0.4526262533345599</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2162,7 +2141,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PT Bank Panin Dubai Syariah Tbk (IDX:PNBS)</t>
+          <t>PT Bank Mandiri (Persero) Tbk (IDX:BMRI)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2171,10 +2150,13 @@
         </is>
       </c>
       <c r="D15">
-        <v>-0.024</v>
+        <v>0.129</v>
       </c>
       <c r="E15">
-        <v>-0.396</v>
+        <v>0.185</v>
+      </c>
+      <c r="F15">
+        <v>0.269</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2189,82 +2171,85 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>0.164</v>
+        <v>2590.8</v>
       </c>
       <c r="L15">
-        <v>0.009879518072289156</v>
+        <v>0.3851116330231591</v>
       </c>
       <c r="M15">
-        <v>-0</v>
+        <v>1104.3</v>
       </c>
       <c r="N15">
-        <v>-0</v>
+        <v>0.03725369146535235</v>
       </c>
       <c r="O15">
-        <v>-0</v>
+        <v>0.4262389995368225</v>
       </c>
       <c r="P15">
-        <v>-0</v>
+        <v>1104.3</v>
       </c>
       <c r="Q15">
-        <v>-0</v>
+        <v>0.03725369146535235</v>
       </c>
       <c r="R15">
-        <v>-0</v>
+        <v>0.4262389995368225</v>
       </c>
       <c r="S15">
         <v>0</v>
       </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
       <c r="U15">
-        <v>3.94</v>
+        <v>3508.1</v>
       </c>
       <c r="V15">
-        <v>0.01706366392377653</v>
+        <v>0.118346169545959</v>
       </c>
       <c r="W15">
-        <v>0.001490909090909091</v>
+        <v>0.1886770467687199</v>
       </c>
       <c r="X15">
-        <v>0.04990725541190267</v>
+        <v>0.09069443576843639</v>
       </c>
       <c r="Y15">
-        <v>-0.04841634632099358</v>
+        <v>0.09798261100028349</v>
       </c>
       <c r="Z15">
-        <v>0.2369296204844212</v>
+        <v>0.3854779654024444</v>
       </c>
       <c r="AA15">
         <v>0</v>
       </c>
       <c r="AB15">
-        <v>0.04986720277382792</v>
+        <v>0.08605246223098816</v>
       </c>
       <c r="AC15">
-        <v>-0.04986720277382792</v>
+        <v>-0.08605246223098816</v>
       </c>
       <c r="AD15">
-        <v>0.437</v>
+        <v>9499.4</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>0.437</v>
+        <v>9499.4</v>
       </c>
       <c r="AG15">
-        <v>-3.503</v>
+        <v>5991.299999999999</v>
       </c>
       <c r="AH15">
-        <v>0.001889019050130329</v>
+        <v>0.2426900958303208</v>
       </c>
       <c r="AI15">
-        <v>0.001996920082070217</v>
+        <v>0.3846783076324997</v>
       </c>
       <c r="AJ15">
-        <v>-0.01540477666811787</v>
+        <v>0.1681343660548914</v>
       </c>
       <c r="AK15">
-        <v>-0.01630083249184493</v>
+        <v>0.2827912377338185</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2281,7 +2266,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PT Bank Syariah Indonesia Tbk (IDX:BRIS)</t>
+          <t>PT Bank OCBC NISP Tbk (IDX:NISP)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2290,10 +2275,10 @@
         </is>
       </c>
       <c r="D16">
-        <v>0.193</v>
+        <v>0.0619</v>
       </c>
       <c r="E16">
-        <v>0.401</v>
+        <v>0.0762</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2308,82 +2293,85 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>60.1</v>
+        <v>199.1</v>
       </c>
       <c r="L16">
-        <v>0.2517804775869292</v>
+        <v>0.3731958762886598</v>
       </c>
       <c r="M16">
-        <v>-0</v>
+        <v>33.1</v>
       </c>
       <c r="N16">
-        <v>-0</v>
+        <v>0.03025594149908592</v>
       </c>
       <c r="O16">
-        <v>-0</v>
+        <v>0.1662481165243596</v>
       </c>
       <c r="P16">
-        <v>-0</v>
+        <v>33.1</v>
       </c>
       <c r="Q16">
-        <v>-0</v>
+        <v>0.03025594149908592</v>
       </c>
       <c r="R16">
-        <v>-0</v>
+        <v>0.1662481165243596</v>
       </c>
       <c r="S16">
         <v>0</v>
       </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
       <c r="U16">
-        <v>900.2</v>
+        <v>364</v>
       </c>
       <c r="V16">
-        <v>0.1756590629695397</v>
+        <v>0.3327239488117002</v>
       </c>
       <c r="W16">
-        <v>0.1687728166245437</v>
+        <v>0.08938672892161263</v>
       </c>
       <c r="X16">
-        <v>0.04995488157848862</v>
+        <v>0.11176766052565</v>
       </c>
       <c r="Y16">
-        <v>0.118817935046055</v>
+        <v>-0.02238093160403741</v>
       </c>
       <c r="Z16">
-        <v>6.009566968781466</v>
+        <v>0.2725693557451592</v>
       </c>
       <c r="AA16">
         <v>0</v>
       </c>
       <c r="AB16">
-        <v>0.04987810366203805</v>
+        <v>0.08684926274141132</v>
       </c>
       <c r="AC16">
-        <v>-0.04987810366203805</v>
+        <v>-0.08684926274141132</v>
       </c>
       <c r="AD16">
-        <v>20.5</v>
+        <v>1015.6</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>20.5</v>
+        <v>1015.6</v>
       </c>
       <c r="AG16">
-        <v>-879.7</v>
+        <v>651.6</v>
       </c>
       <c r="AH16">
-        <v>0.003984296042913784</v>
+        <v>0.481418278346606</v>
       </c>
       <c r="AI16">
-        <v>0.01199461704990931</v>
+        <v>0.317931379914851</v>
       </c>
       <c r="AJ16">
-        <v>-0.2072320376914017</v>
+        <v>0.3732813932172319</v>
       </c>
       <c r="AK16">
-        <v>-1.087526270243541</v>
+        <v>0.2302148106274731</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -2400,7 +2388,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PT Bank Mestika Dharma Tbk (IDX:BBMD)</t>
+          <t>PT Bank Pembangunan Daerah Jawa Barat dan Banten Tbk (IDX:BJBR)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2409,10 +2397,10 @@
         </is>
       </c>
       <c r="D17">
-        <v>0.121</v>
+        <v>0.101</v>
       </c>
       <c r="E17">
-        <v>0.215</v>
+        <v>0.182</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2427,85 +2415,85 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>32.2</v>
+        <v>160.6</v>
       </c>
       <c r="L17">
-        <v>0.4756277695716396</v>
+        <v>0.2520006276478896</v>
       </c>
       <c r="M17">
-        <v>4.81</v>
+        <v>68.5</v>
       </c>
       <c r="N17">
-        <v>0.008531394111387017</v>
+        <v>0.07563210776195207</v>
       </c>
       <c r="O17">
-        <v>0.1493788819875776</v>
+        <v>0.4265255292652553</v>
       </c>
       <c r="P17">
-        <v>-0</v>
+        <v>68.5</v>
       </c>
       <c r="Q17">
-        <v>-0</v>
+        <v>0.07563210776195207</v>
       </c>
       <c r="R17">
-        <v>-0</v>
+        <v>0.4265255292652553</v>
       </c>
       <c r="S17">
-        <v>4.81</v>
+        <v>0</v>
       </c>
       <c r="T17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U17">
-        <v>35.9</v>
+        <v>643.6</v>
       </c>
       <c r="V17">
-        <v>0.06367506207875133</v>
+        <v>0.7106105774539031</v>
       </c>
       <c r="W17">
-        <v>0.1402439024390244</v>
+        <v>0.185686206497861</v>
       </c>
       <c r="X17">
-        <v>0.05120715754128519</v>
+        <v>0.1473689809824843</v>
       </c>
       <c r="Y17">
-        <v>0.08903674489773922</v>
+        <v>0.0383172255153767</v>
       </c>
       <c r="Z17">
-        <v>0.3210661102153087</v>
+        <v>0.6238253719655442</v>
       </c>
       <c r="AA17">
         <v>0</v>
       </c>
       <c r="AB17">
-        <v>0.04994507300748068</v>
+        <v>0.08956846807745322</v>
       </c>
       <c r="AC17">
-        <v>-0.04994507300748068</v>
+        <v>-0.08956846807745322</v>
       </c>
       <c r="AD17">
-        <v>33.5</v>
+        <v>1770.9</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>33.5</v>
+        <v>1770.9</v>
       </c>
       <c r="AG17">
-        <v>-2.399999999999999</v>
+        <v>1127.3</v>
       </c>
       <c r="AH17">
-        <v>0.05608571906914449</v>
+        <v>0.6616229544945079</v>
       </c>
       <c r="AI17">
-        <v>0.1032675709001233</v>
+        <v>0.6589150171156422</v>
       </c>
       <c r="AJ17">
-        <v>-0.004275026718916991</v>
+        <v>0.5545007378258732</v>
       </c>
       <c r="AK17">
-        <v>-0.008318890814558054</v>
+        <v>0.5515166340508807</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -2522,7 +2510,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PT Bank Ina Perdana Tbk (IDX:BINA)</t>
+          <t>PT Bank BTPN Tbk (IDX:BTPN)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2531,10 +2519,10 @@
         </is>
       </c>
       <c r="D18">
-        <v>0.191</v>
+        <v>0.0547</v>
       </c>
       <c r="E18">
-        <v>0.078</v>
+        <v>0.12</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -2543,16 +2531,16 @@
         <v>0</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>-0.006756577586524283</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>-0.005237866340802041</v>
       </c>
       <c r="K18">
-        <v>2.75</v>
+        <v>199.4</v>
       </c>
       <c r="L18">
-        <v>0.1627218934911243</v>
+        <v>0.2590283190439076</v>
       </c>
       <c r="M18">
         <v>-0</v>
@@ -2576,61 +2564,67 @@
         <v>0</v>
       </c>
       <c r="U18">
-        <v>304.6</v>
+        <v>959.3</v>
       </c>
       <c r="V18">
-        <v>0.1943097729012503</v>
+        <v>0.7020638173302107</v>
       </c>
       <c r="W18">
-        <v>0.0355297157622739</v>
+        <v>0.08556470992104359</v>
       </c>
       <c r="X18">
-        <v>0.05078704713073354</v>
+        <v>0.1713882902887746</v>
       </c>
       <c r="Y18">
-        <v>-0.01525733136845964</v>
+        <v>-0.08582358036773105</v>
       </c>
       <c r="Z18">
-        <v>0.3526711185308848</v>
+        <v>0.189436255433076</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>-0.0009922417860604867</v>
       </c>
       <c r="AB18">
-        <v>0.04999852841528081</v>
+        <v>0.0905381915820159</v>
       </c>
       <c r="AC18">
-        <v>-0.04999852841528081</v>
+        <v>-0.09153043336807638</v>
       </c>
       <c r="AD18">
-        <v>64</v>
+        <v>3591</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>27.41606713053196</v>
       </c>
       <c r="AF18">
-        <v>64</v>
+        <v>3618.416067130532</v>
       </c>
       <c r="AG18">
-        <v>-240.6</v>
+        <v>2659.116067130532</v>
       </c>
       <c r="AH18">
-        <v>0.03922530031870557</v>
+        <v>0.7258875790804139</v>
       </c>
       <c r="AI18">
-        <v>0.4330175913396481</v>
+        <v>0.5880623780948697</v>
       </c>
       <c r="AJ18">
-        <v>-0.1813112283345893</v>
+        <v>0.6605652599036831</v>
       </c>
       <c r="AK18">
-        <v>1.534438775510204</v>
+        <v>0.5119773270291481</v>
       </c>
       <c r="AL18">
         <v>0</v>
       </c>
       <c r="AM18">
         <v>0</v>
+      </c>
+      <c r="AN18">
+        <v>12734.04255319149</v>
+      </c>
+      <c r="AP18">
+        <v>9429.489599753662</v>
       </c>
     </row>
     <row r="19">
@@ -2641,7 +2635,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PT Bank JTrust Indonesia Tbk (IDX:BCIC)</t>
+          <t>PT Bank Nationalnobu Tbk (IDX:NOBU)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2650,7 +2644,10 @@
         </is>
       </c>
       <c r="D19">
-        <v>-0.245</v>
+        <v>0.133</v>
+      </c>
+      <c r="E19">
+        <v>0.25</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2665,10 +2662,10 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>-28.2</v>
+        <v>5.84</v>
       </c>
       <c r="L19">
-        <v>-4.615384615384615</v>
+        <v>0.1361305361305361</v>
       </c>
       <c r="M19">
         <v>-0</v>
@@ -2677,7 +2674,7 @@
         <v>-0</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P19">
         <v>-0</v>
@@ -2686,61 +2683,61 @@
         <v>-0</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S19">
         <v>0</v>
       </c>
       <c r="U19">
-        <v>165.2</v>
+        <v>112.3</v>
       </c>
       <c r="V19">
-        <v>0.8186323092170464</v>
+        <v>0.6932098765432099</v>
       </c>
       <c r="W19">
-        <v>-0.2761998041136141</v>
+        <v>0.05372585096596136</v>
       </c>
       <c r="X19">
-        <v>0.05184647792073496</v>
+        <v>0.1294242623686088</v>
       </c>
       <c r="Y19">
-        <v>-0.328046282034349</v>
+        <v>-0.07569841140264741</v>
       </c>
       <c r="Z19">
-        <v>0.2909523809523814</v>
+        <v>0.3672945205479452</v>
       </c>
       <c r="AA19">
         <v>0</v>
       </c>
       <c r="AB19">
-        <v>0.05014004230652212</v>
+        <v>0.09234427535143941</v>
       </c>
       <c r="AC19">
-        <v>-0.05014004230652212</v>
+        <v>-0.09234427535143941</v>
       </c>
       <c r="AD19">
-        <v>17.7</v>
+        <v>232.9</v>
       </c>
       <c r="AE19">
         <v>0</v>
       </c>
       <c r="AF19">
-        <v>17.7</v>
+        <v>232.9</v>
       </c>
       <c r="AG19">
-        <v>-147.5</v>
+        <v>120.6</v>
       </c>
       <c r="AH19">
-        <v>0.0806378132118451</v>
+        <v>0.5897695619144088</v>
       </c>
       <c r="AI19">
-        <v>0.1498729889923793</v>
+        <v>0.6656187482137754</v>
       </c>
       <c r="AJ19">
-        <v>-2.716390423572744</v>
+        <v>0.4267515923566879</v>
       </c>
       <c r="AK19">
-        <v>3.131634819532909</v>
+        <v>0.5075757575757576</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -2757,7 +2754,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PT Bank Nationalnobu Tbk (IDX:NOBU)</t>
+          <t>PT Bank KB Bukopin Tbk (IDX:BBKP)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2765,29 +2762,8 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D20">
-        <v>0.136</v>
-      </c>
-      <c r="E20">
-        <v>0.121</v>
-      </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="H20">
-        <v>0</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20">
-        <v>0</v>
-      </c>
       <c r="K20">
-        <v>3.51</v>
-      </c>
-      <c r="L20">
-        <v>0.09310344827586206</v>
+        <v>-386.3</v>
       </c>
       <c r="M20">
         <v>-0</v>
@@ -2796,7 +2772,7 @@
         <v>-0</v>
       </c>
       <c r="O20">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P20">
         <v>-0</v>
@@ -2805,670 +2781,66 @@
         <v>-0</v>
       </c>
       <c r="R20">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S20">
         <v>0</v>
       </c>
       <c r="U20">
-        <v>106.2</v>
+        <v>1091.6</v>
       </c>
       <c r="V20">
-        <v>0.4862637362637363</v>
+        <v>2.462996389891697</v>
       </c>
       <c r="W20">
-        <v>0.03513513513513513</v>
+        <v>-0.6530853761622992</v>
       </c>
       <c r="X20">
-        <v>0.06169062269089397</v>
+        <v>0.196390966859342</v>
       </c>
       <c r="Y20">
-        <v>-0.02655548755575884</v>
+        <v>-0.8494763430216412</v>
       </c>
       <c r="Z20">
-        <v>0.4259887005649716</v>
+        <v>0</v>
       </c>
       <c r="AA20">
         <v>0</v>
       </c>
       <c r="AB20">
-        <v>0.05035810783941238</v>
+        <v>0.09626800013532681</v>
       </c>
       <c r="AC20">
-        <v>-0.05035810783941238</v>
+        <v>-0.09626800013532681</v>
       </c>
       <c r="AD20">
-        <v>114.3</v>
+        <v>1493.3</v>
       </c>
       <c r="AE20">
         <v>0</v>
       </c>
       <c r="AF20">
-        <v>114.3</v>
+        <v>1493.3</v>
       </c>
       <c r="AG20">
-        <v>8.099999999999994</v>
+        <v>401.7</v>
       </c>
       <c r="AH20">
-        <v>0.3435527502254283</v>
+        <v>0.771133488252001</v>
       </c>
       <c r="AI20">
-        <v>0.5125560538116591</v>
+        <v>0.6940739019288868</v>
       </c>
       <c r="AJ20">
-        <v>0.03576158940397348</v>
+        <v>0.4754408805775832</v>
       </c>
       <c r="AK20">
-        <v>0.06934931506849311</v>
+        <v>0.3789980186810076</v>
       </c>
       <c r="AL20">
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>PT Bank Mega Tbk (IDX:MEGA)</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D21">
-        <v>0.103</v>
-      </c>
-      <c r="E21">
-        <v>0.229</v>
-      </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
-      <c r="K21">
-        <v>264.2</v>
-      </c>
-      <c r="L21">
-        <v>0.4987728903152727</v>
-      </c>
-      <c r="M21">
-        <v>147</v>
-      </c>
-      <c r="N21">
-        <v>0.03558202018735022</v>
-      </c>
-      <c r="O21">
-        <v>0.5563966691900076</v>
-      </c>
-      <c r="P21">
-        <v>147</v>
-      </c>
-      <c r="Q21">
-        <v>0.03558202018735022</v>
-      </c>
-      <c r="R21">
-        <v>0.5563966691900076</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-      <c r="T21">
-        <v>0</v>
-      </c>
-      <c r="U21">
-        <v>444.9</v>
-      </c>
-      <c r="V21">
-        <v>0.1076900733425314</v>
-      </c>
-      <c r="W21">
-        <v>0.2450153018640452</v>
-      </c>
-      <c r="X21">
-        <v>0.05407013089484793</v>
-      </c>
-      <c r="Y21">
-        <v>0.1909451709691973</v>
-      </c>
-      <c r="Z21">
-        <v>0.3583654691834111</v>
-      </c>
-      <c r="AA21">
-        <v>0</v>
-      </c>
-      <c r="AB21">
-        <v>0.05040068458471333</v>
-      </c>
-      <c r="AC21">
-        <v>-0.05040068458471333</v>
-      </c>
-      <c r="AD21">
-        <v>768.9</v>
-      </c>
-      <c r="AE21">
-        <v>0</v>
-      </c>
-      <c r="AF21">
-        <v>768.9</v>
-      </c>
-      <c r="AG21">
-        <v>324</v>
-      </c>
-      <c r="AH21">
-        <v>0.1569119627770295</v>
-      </c>
-      <c r="AI21">
-        <v>0.3750182900063405</v>
-      </c>
-      <c r="AJ21">
-        <v>0.07272237559760285</v>
-      </c>
-      <c r="AK21">
-        <v>0.2018188613429675</v>
-      </c>
-      <c r="AL21">
-        <v>0</v>
-      </c>
-      <c r="AM21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>PT Bank KB Bukopin Tbk (IDX:BBKP)</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="G22">
-        <v>-0</v>
-      </c>
-      <c r="H22">
-        <v>-0</v>
-      </c>
-      <c r="I22">
-        <v>-0</v>
-      </c>
-      <c r="J22">
-        <v>-0</v>
-      </c>
-      <c r="K22">
-        <v>-179</v>
-      </c>
-      <c r="L22">
-        <v>8.774509803921569</v>
-      </c>
-      <c r="M22">
-        <v>-0</v>
-      </c>
-      <c r="N22">
-        <v>-0</v>
-      </c>
-      <c r="O22">
-        <v>0</v>
-      </c>
-      <c r="P22">
-        <v>-0</v>
-      </c>
-      <c r="Q22">
-        <v>-0</v>
-      </c>
-      <c r="R22">
-        <v>0</v>
-      </c>
-      <c r="S22">
-        <v>0</v>
-      </c>
-      <c r="U22">
-        <v>859.3</v>
-      </c>
-      <c r="V22">
-        <v>0.6783768848188205</v>
-      </c>
-      <c r="W22">
-        <v>-0.2575169040425838</v>
-      </c>
-      <c r="X22">
-        <v>0.07323027583844922</v>
-      </c>
-      <c r="Y22">
-        <v>-0.330747179881033</v>
-      </c>
-      <c r="Z22">
-        <v>-0.01455064194008559</v>
-      </c>
-      <c r="AA22">
-        <v>0</v>
-      </c>
-      <c r="AB22">
-        <v>0.05059490999117494</v>
-      </c>
-      <c r="AC22">
-        <v>-0.05059490999117494</v>
-      </c>
-      <c r="AD22">
-        <v>1309.8</v>
-      </c>
-      <c r="AE22">
-        <v>0</v>
-      </c>
-      <c r="AF22">
-        <v>1309.8</v>
-      </c>
-      <c r="AG22">
-        <v>450.5</v>
-      </c>
-      <c r="AH22">
-        <v>0.5083640597710072</v>
-      </c>
-      <c r="AI22">
-        <v>0.6981132075471699</v>
-      </c>
-      <c r="AJ22">
-        <v>0.2623456790123457</v>
-      </c>
-      <c r="AK22">
-        <v>0.4430130789654834</v>
-      </c>
-      <c r="AL22">
-        <v>0</v>
-      </c>
-      <c r="AM22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>PT Bank Rakyat Indonesia (Persero) Tbk (IDX:BBRI)</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D23">
-        <v>0.046</v>
-      </c>
-      <c r="E23">
-        <v>-0.0171</v>
-      </c>
-      <c r="F23">
-        <v>0.291</v>
-      </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-      <c r="H23">
-        <v>0</v>
-      </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-      <c r="J23">
-        <v>0</v>
-      </c>
-      <c r="K23">
-        <v>1665.7</v>
-      </c>
-      <c r="L23">
-        <v>0.2975899094206135</v>
-      </c>
-      <c r="M23">
-        <v>848.8</v>
-      </c>
-      <c r="N23">
-        <v>0.01966294086986738</v>
-      </c>
-      <c r="O23">
-        <v>0.5095755538212162</v>
-      </c>
-      <c r="P23">
-        <v>848.8</v>
-      </c>
-      <c r="Q23">
-        <v>0.01966294086986738</v>
-      </c>
-      <c r="R23">
-        <v>0.5095755538212162</v>
-      </c>
-      <c r="S23">
-        <v>0</v>
-      </c>
-      <c r="T23">
-        <v>0</v>
-      </c>
-      <c r="U23">
-        <v>7932.8</v>
-      </c>
-      <c r="V23">
-        <v>0.1837678809289396</v>
-      </c>
-      <c r="W23">
-        <v>0.1288613137556764</v>
-      </c>
-      <c r="X23">
-        <v>0.05456132867410577</v>
-      </c>
-      <c r="Y23">
-        <v>0.07429998508157065</v>
-      </c>
-      <c r="Z23">
-        <v>0.4737332103289802</v>
-      </c>
-      <c r="AA23">
-        <v>0</v>
-      </c>
-      <c r="AB23">
-        <v>0.05063030876649659</v>
-      </c>
-      <c r="AC23">
-        <v>-0.05063030876649659</v>
-      </c>
-      <c r="AD23">
-        <v>8972.5</v>
-      </c>
-      <c r="AE23">
-        <v>0</v>
-      </c>
-      <c r="AF23">
-        <v>8972.5</v>
-      </c>
-      <c r="AG23">
-        <v>1039.7</v>
-      </c>
-      <c r="AH23">
-        <v>0.1720847717683161</v>
-      </c>
-      <c r="AI23">
-        <v>0.3137961907293291</v>
-      </c>
-      <c r="AJ23">
-        <v>0.02351879331873541</v>
-      </c>
-      <c r="AK23">
-        <v>0.05032283670367751</v>
-      </c>
-      <c r="AL23">
-        <v>0</v>
-      </c>
-      <c r="AM23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>PT Bank Mandiri (Persero) Tbk (IDX:BMRI)</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D24">
-        <v>0.0776</v>
-      </c>
-      <c r="E24">
-        <v>0.0467</v>
-      </c>
-      <c r="F24">
-        <v>0.273</v>
-      </c>
-      <c r="G24">
-        <v>0</v>
-      </c>
-      <c r="H24">
-        <v>0</v>
-      </c>
-      <c r="I24">
-        <v>0</v>
-      </c>
-      <c r="J24">
-        <v>0</v>
-      </c>
-      <c r="K24">
-        <v>1562.5</v>
-      </c>
-      <c r="L24">
-        <v>0.2792622115779879</v>
-      </c>
-      <c r="M24">
-        <v>719</v>
-      </c>
-      <c r="N24">
-        <v>0.03135507110492828</v>
-      </c>
-      <c r="O24">
-        <v>0.46016</v>
-      </c>
-      <c r="P24">
-        <v>719</v>
-      </c>
-      <c r="Q24">
-        <v>0.03135507110492828</v>
-      </c>
-      <c r="R24">
-        <v>0.46016</v>
-      </c>
-      <c r="S24">
-        <v>0</v>
-      </c>
-      <c r="T24">
-        <v>0</v>
-      </c>
-      <c r="U24">
-        <v>3371.9</v>
-      </c>
-      <c r="V24">
-        <v>0.1470461255336685</v>
-      </c>
-      <c r="W24">
-        <v>0.1255352824443427</v>
-      </c>
-      <c r="X24">
-        <v>0.05690808428621595</v>
-      </c>
-      <c r="Y24">
-        <v>0.06862719815812672</v>
-      </c>
-      <c r="Z24">
-        <v>0.3252133175234243</v>
-      </c>
-      <c r="AA24">
-        <v>0</v>
-      </c>
-      <c r="AB24">
-        <v>0.05092201947022747</v>
-      </c>
-      <c r="AC24">
-        <v>-0.05092201947022747</v>
-      </c>
-      <c r="AD24">
-        <v>7147.7</v>
-      </c>
-      <c r="AE24">
-        <v>0</v>
-      </c>
-      <c r="AF24">
-        <v>7147.7</v>
-      </c>
-      <c r="AG24">
-        <v>3775.8</v>
-      </c>
-      <c r="AH24">
-        <v>0.2376340654152786</v>
-      </c>
-      <c r="AI24">
-        <v>0.3242131332695282</v>
-      </c>
-      <c r="AJ24">
-        <v>0.1413802528953409</v>
-      </c>
-      <c r="AK24">
-        <v>0.2021912350597609</v>
-      </c>
-      <c r="AL24">
-        <v>0</v>
-      </c>
-      <c r="AM24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>PT Bank Capital Indonesia Tbk (IDX:BACA)</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D25">
-        <v>-0.00331</v>
-      </c>
-      <c r="E25">
-        <v>-0.294</v>
-      </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
-      <c r="H25">
-        <v>0</v>
-      </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
-      <c r="K25">
-        <v>1.53</v>
-      </c>
-      <c r="L25">
-        <v>0.05257731958762887</v>
-      </c>
-      <c r="M25">
-        <v>-0</v>
-      </c>
-      <c r="N25">
-        <v>-0</v>
-      </c>
-      <c r="O25">
-        <v>-0</v>
-      </c>
-      <c r="P25">
-        <v>-0</v>
-      </c>
-      <c r="Q25">
-        <v>-0</v>
-      </c>
-      <c r="R25">
-        <v>-0</v>
-      </c>
-      <c r="S25">
-        <v>0</v>
-      </c>
-      <c r="U25">
-        <v>219</v>
-      </c>
-      <c r="V25">
-        <v>1.67816091954023</v>
-      </c>
-      <c r="W25">
-        <v>0.01403669724770642</v>
-      </c>
-      <c r="X25">
-        <v>0.06193349364961458</v>
-      </c>
-      <c r="Y25">
-        <v>-0.04789679640190815</v>
-      </c>
-      <c r="Z25">
-        <v>0.2844574780058651</v>
-      </c>
-      <c r="AA25">
-        <v>0</v>
-      </c>
-      <c r="AB25">
-        <v>0.05105418514406759</v>
-      </c>
-      <c r="AC25">
-        <v>-0.05105418514406759</v>
-      </c>
-      <c r="AD25">
-        <v>69.7</v>
-      </c>
-      <c r="AE25">
-        <v>0</v>
-      </c>
-      <c r="AF25">
-        <v>69.7</v>
-      </c>
-      <c r="AG25">
-        <v>-149.3</v>
-      </c>
-      <c r="AH25">
-        <v>0.3481518481518482</v>
-      </c>
-      <c r="AI25">
-        <v>0.3741277509393451</v>
-      </c>
-      <c r="AJ25">
-        <v>7.941489361702123</v>
-      </c>
-      <c r="AK25">
-        <v>4.565749235474004</v>
-      </c>
-      <c r="AL25">
-        <v>0</v>
-      </c>
-      <c r="AM25">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/indonesia/indonesia_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/indonesia/indonesia_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ20"/>
+  <dimension ref="A1:AQ25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.129</v>
+        <v>0.109</v>
       </c>
       <c r="E2">
-        <v>0.161</v>
+        <v>0.1265</v>
       </c>
       <c r="F2">
-        <v>0.2475</v>
+        <v>0.196</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,91 +603,91 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>-0.0002036751178265999</v>
+        <v>-0.0001345625316495519</v>
       </c>
       <c r="J2">
-        <v>-0.0001696105769869465</v>
+        <v>-0.0001112869882987137</v>
       </c>
       <c r="K2">
-        <v>9417.780000000001</v>
+        <v>11135.83</v>
       </c>
       <c r="L2">
-        <v>0.3828471681331029</v>
+        <v>0.3913597992563488</v>
       </c>
       <c r="M2">
-        <v>4477.2</v>
+        <v>6654.04</v>
       </c>
       <c r="N2">
-        <v>0.02675966684896137</v>
+        <v>0.03441280847996012</v>
       </c>
       <c r="O2">
-        <v>0.4753986608308964</v>
+        <v>0.5975342655194987</v>
       </c>
       <c r="P2">
-        <v>4395.9</v>
+        <v>6522.52</v>
       </c>
       <c r="Q2">
-        <v>0.02627374687334702</v>
+        <v>0.03373262432547888</v>
       </c>
       <c r="R2">
-        <v>0.4667660531462828</v>
+        <v>0.5857237403947438</v>
       </c>
       <c r="S2">
-        <v>81.29999999999995</v>
+        <v>131.5200000000002</v>
       </c>
       <c r="T2">
-        <v>0.01815867059769498</v>
+        <v>0.01976543573528265</v>
       </c>
       <c r="U2">
-        <v>16558</v>
+        <v>13841.14</v>
       </c>
       <c r="V2">
-        <v>0.09896510401257534</v>
+        <v>0.07158245215903648</v>
       </c>
       <c r="W2">
-        <v>0.0878651706282072</v>
+        <v>0.08089330024813896</v>
       </c>
       <c r="X2">
-        <v>0.08523105886317225</v>
+        <v>0.07103877599054217</v>
       </c>
       <c r="Y2">
-        <v>0.002634111765034947</v>
+        <v>0.009854524257596781</v>
       </c>
       <c r="Z2">
-        <v>0.4083747943426618</v>
+        <v>0.3716699402288084</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.08307327416953508</v>
+        <v>0.06861928395501266</v>
       </c>
       <c r="AC2">
-        <v>-0.08307327416953508</v>
+        <v>-0.06861928395501266</v>
       </c>
       <c r="AD2">
-        <v>30013.769</v>
+        <v>31543.639</v>
       </c>
       <c r="AE2">
-        <v>27.61134699727118</v>
+        <v>21.6443459403134</v>
       </c>
       <c r="AF2">
-        <v>30041.38034699727</v>
+        <v>31565.28334594031</v>
       </c>
       <c r="AG2">
-        <v>13483.38034699727</v>
+        <v>17724.14334594031</v>
       </c>
       <c r="AH2">
-        <v>0.1522216462925536</v>
+        <v>0.140337124749408</v>
       </c>
       <c r="AI2">
-        <v>0.3220159872440643</v>
+        <v>0.3079549352304464</v>
       </c>
       <c r="AJ2">
-        <v>0.07457833054298217</v>
+        <v>0.08396743329674258</v>
       </c>
       <c r="AK2">
-        <v>0.1757168150635487</v>
+        <v>0.1999146689877564</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -696,10 +696,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>58620.642578125</v>
+        <v>63087.278</v>
       </c>
       <c r="AP2">
-        <v>26334.72724022905</v>
+        <v>35448.28669188062</v>
       </c>
     </row>
     <row r="3">
@@ -719,10 +719,7 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.436</v>
-      </c>
-      <c r="E3">
-        <v>0.97</v>
+        <v>0.629</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -731,16 +728,16 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.004482254146764264</v>
+        <v>0.00255912681763219</v>
       </c>
       <c r="J3">
-        <v>0.003522983846415093</v>
+        <v>0.001970375320599546</v>
       </c>
       <c r="K3">
-        <v>20.7</v>
+        <v>25.8</v>
       </c>
       <c r="L3">
-        <v>0.4859154929577464</v>
+        <v>0.3845007451564829</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -764,55 +761,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>22.2</v>
+        <v>66</v>
       </c>
       <c r="V3">
-        <v>0.009044243461256417</v>
+        <v>0.03658739397971063</v>
       </c>
       <c r="W3">
-        <v>0.2297447280799112</v>
+        <v>0.06221364842054498</v>
       </c>
       <c r="X3">
-        <v>0.07962605675209722</v>
+        <v>0.06789544945649974</v>
       </c>
       <c r="Y3">
-        <v>0.150118671327814</v>
+        <v>-0.00568180103595476</v>
       </c>
       <c r="Z3">
-        <v>0.1351543082054109</v>
+        <v>0.1696945240561605</v>
       </c>
       <c r="AA3">
-        <v>0.0004761464445810694</v>
+        <v>0.0003343619022411446</v>
       </c>
       <c r="AB3">
-        <v>0.07971087659065892</v>
+        <v>0.06788376944218595</v>
       </c>
       <c r="AC3">
-        <v>-0.07923473014607786</v>
+        <v>-0.0675494075399448</v>
       </c>
       <c r="AD3">
-        <v>2.72</v>
+        <v>1.92</v>
       </c>
       <c r="AE3">
-        <v>0.1952798667392118</v>
+        <v>0.1964129526844003</v>
       </c>
       <c r="AF3">
-        <v>2.915279866739212</v>
+        <v>2.1164129526844</v>
       </c>
       <c r="AG3">
-        <v>-19.28472013326079</v>
+        <v>-63.8835870473156</v>
       </c>
       <c r="AH3">
-        <v>0.001186271308513408</v>
+        <v>0.001171868061389455</v>
       </c>
       <c r="AI3">
-        <v>0.006980778738913662</v>
+        <v>0.004781596187465927</v>
       </c>
       <c r="AJ3">
-        <v>-0.007918777618935668</v>
+        <v>-0.03671435888291977</v>
       </c>
       <c r="AK3">
-        <v>-0.04877080152228822</v>
+        <v>-0.1696250743467771</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -821,10 +818,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>11.82608695652174</v>
+        <v>9.099526066350711</v>
       </c>
       <c r="AP3">
-        <v>-83.8466092750469</v>
+        <v>-302.7658153901214</v>
       </c>
     </row>
     <row r="4">
@@ -835,7 +832,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PT Bank Bisnis Internasional, Tbk (IDX:BBSI)</t>
+          <t>PT Krom Bank Indonesia Tbk (IDX:BBSI)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -844,10 +841,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.23</v>
+        <v>0.356</v>
       </c>
       <c r="E4">
-        <v>0.315</v>
+        <v>0.365</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -862,10 +859,10 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>5.2</v>
+        <v>7.22</v>
       </c>
       <c r="L4">
-        <v>0.6088992974238877</v>
+        <v>0.4688311688311688</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -889,55 +886,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>20.5</v>
+        <v>6.84</v>
       </c>
       <c r="V4">
-        <v>0.03064733143967708</v>
+        <v>0.007902946273830156</v>
       </c>
       <c r="W4">
-        <v>0.06961178045515395</v>
+        <v>0.0514978601997147</v>
       </c>
       <c r="X4">
-        <v>0.07959068789865785</v>
+        <v>0.06786884769647322</v>
       </c>
       <c r="Y4">
-        <v>-0.009978907443503895</v>
+        <v>-0.01637098749675853</v>
       </c>
       <c r="Z4">
-        <v>0.1721149582812689</v>
+        <v>0.12853470437018</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.07958904586124638</v>
+        <v>0.06786884769647322</v>
       </c>
       <c r="AC4">
-        <v>-0.07958904586124638</v>
+        <v>-0.06786884769647322</v>
       </c>
       <c r="AD4">
-        <v>0.112</v>
+        <v>0</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.112</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>-20.388</v>
+        <v>-6.84</v>
       </c>
       <c r="AH4">
-        <v>0.0001674110479333704</v>
+        <v>0</v>
       </c>
       <c r="AI4">
-        <v>0.0007982211072467075</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
-        <v>-0.03143812296457121</v>
+        <v>-0.007965900356369227</v>
       </c>
       <c r="AK4">
-        <v>-0.1701665943311188</v>
+        <v>-0.03463992707383774</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -954,7 +951,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PT Bank Jago Tbk (IDX:ARTO)</t>
+          <t>PT Bank JTrust Indonesia Tbk (IDX:BCIC)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -963,10 +960,7 @@
         </is>
       </c>
       <c r="D5">
-        <v>1.916</v>
-      </c>
-      <c r="F5">
-        <v>2.26</v>
+        <v>0.171</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -981,10 +975,10 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>10.5</v>
+        <v>7.3</v>
       </c>
       <c r="L5">
-        <v>0.1586102719033232</v>
+        <v>0.1341911764705882</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -1008,55 +1002,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>38.8</v>
+        <v>42.6</v>
       </c>
       <c r="V5">
-        <v>0.01176149625632786</v>
+        <v>0.3014861995753715</v>
       </c>
       <c r="W5">
-        <v>0.01844370279290357</v>
+        <v>0.03362505757715339</v>
       </c>
       <c r="X5">
-        <v>0.07962670788927217</v>
+        <v>0.06787221746098325</v>
       </c>
       <c r="Y5">
-        <v>-0.06118300509636861</v>
+        <v>-0.03424715988382986</v>
       </c>
       <c r="Z5">
-        <v>0.1629137443090931</v>
+        <v>0.2958821257825375</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.07961095307521798</v>
+        <v>0.06787043048350719</v>
       </c>
       <c r="AC5">
-        <v>-0.07961095307521798</v>
+        <v>-0.06787043048350719</v>
       </c>
       <c r="AD5">
-        <v>3.98</v>
+        <v>0.021</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>3.98</v>
+        <v>0.021</v>
       </c>
       <c r="AG5">
-        <v>-34.82</v>
+        <v>-42.579</v>
       </c>
       <c r="AH5">
-        <v>0.001205008961875696</v>
+        <v>0.0001485978729275904</v>
       </c>
       <c r="AI5">
-        <v>0.007259064711461298</v>
+        <v>8.518544059126809e-05</v>
       </c>
       <c r="AJ5">
-        <v>-0.01066763069532609</v>
+        <v>-0.4313064089707357</v>
       </c>
       <c r="AK5">
-        <v>-0.06834419408023867</v>
+        <v>-0.2088014476194213</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1073,7 +1067,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PT Bank Aladin Syariah Tbk (IDX:BANK)</t>
+          <t>PT Bank Maspion Indonesia Tbk (IDX:BMAS)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1081,6 +1075,12 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
+      <c r="D6">
+        <v>0.115</v>
+      </c>
+      <c r="E6">
+        <v>0.0442</v>
+      </c>
       <c r="G6">
         <v>0</v>
       </c>
@@ -1094,10 +1094,10 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>-13.6</v>
+        <v>4.91</v>
       </c>
       <c r="L6">
-        <v>-3.908045977011494</v>
+        <v>0.1647651006711409</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1106,7 +1106,7 @@
         <v>-0</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P6">
         <v>-0</v>
@@ -1115,61 +1115,61 @@
         <v>-0</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
       <c r="U6">
-        <v>31.8</v>
+        <v>248.1</v>
       </c>
       <c r="V6">
-        <v>0.02549915804666827</v>
+        <v>0.3672291296625222</v>
       </c>
       <c r="W6">
-        <v>-0.1763942931258106</v>
+        <v>0.05296655879180151</v>
       </c>
       <c r="X6">
-        <v>0.0796257466351912</v>
+        <v>0.06788710479158064</v>
       </c>
       <c r="Y6">
-        <v>-0.2560200397610018</v>
+        <v>-0.01492054599977913</v>
       </c>
       <c r="Z6">
-        <v>0.04620286776420606</v>
+        <v>0.7104880432968553</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.0796141574493949</v>
+        <v>0.06787741747487895</v>
       </c>
       <c r="AC6">
-        <v>-0.0796141574493949</v>
+        <v>-0.06787741747487895</v>
       </c>
       <c r="AD6">
-        <v>1.47</v>
+        <v>0.544</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>1.47</v>
+        <v>0.544</v>
       </c>
       <c r="AG6">
-        <v>-30.33</v>
+        <v>-247.556</v>
       </c>
       <c r="AH6">
-        <v>0.001177346884836253</v>
+        <v>0.0008045623417496865</v>
       </c>
       <c r="AI6">
-        <v>0.01098080227085979</v>
+        <v>0.002618607516943931</v>
       </c>
       <c r="AJ6">
-        <v>-0.02492665006533692</v>
+        <v>-0.5783424133967535</v>
       </c>
       <c r="AK6">
-        <v>-0.2971490153816009</v>
+        <v>6.134304688274359</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0824</v>
+        <v>0.103</v>
       </c>
       <c r="E7">
-        <v>0.107</v>
+        <v>0.141</v>
       </c>
       <c r="F7">
-        <v>0.148</v>
+        <v>0.13</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1216,28 +1216,28 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>2441.5</v>
+        <v>3115.6</v>
       </c>
       <c r="L7">
-        <v>0.4759444812663262</v>
+        <v>0.502508024064128</v>
       </c>
       <c r="M7">
-        <v>1173.8</v>
+        <v>1633.5</v>
       </c>
       <c r="N7">
-        <v>0.01740094668977305</v>
+        <v>0.02168715008145128</v>
       </c>
       <c r="O7">
-        <v>0.4807700184312922</v>
+        <v>0.5242970856335858</v>
       </c>
       <c r="P7">
-        <v>1173.8</v>
+        <v>1633.5</v>
       </c>
       <c r="Q7">
-        <v>0.01740094668977305</v>
+        <v>0.02168715008145128</v>
       </c>
       <c r="R7">
-        <v>0.4807700184312922</v>
+        <v>0.5242970856335858</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1246,55 +1246,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>3384.7</v>
+        <v>1574.2</v>
       </c>
       <c r="V7">
-        <v>0.05017633690652142</v>
+        <v>0.02089985409135023</v>
       </c>
       <c r="W7">
-        <v>0.1763083211172813</v>
+        <v>0.2238556104009944</v>
       </c>
       <c r="X7">
-        <v>0.07968787316317813</v>
+        <v>0.06790837257022023</v>
       </c>
       <c r="Y7">
-        <v>0.09662044795410318</v>
+        <v>0.1559472378307742</v>
       </c>
       <c r="Z7">
-        <v>0.761900518350191</v>
+        <v>0.5817593244194231</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.0796295787975931</v>
+        <v>0.06787949426233597</v>
       </c>
       <c r="AC7">
-        <v>-0.0796295787975931</v>
+        <v>-0.06787949426233597</v>
       </c>
       <c r="AD7">
-        <v>200.4</v>
+        <v>131.3</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>200.4</v>
+        <v>131.3</v>
       </c>
       <c r="AG7">
-        <v>-3184.3</v>
+        <v>-1442.9</v>
       </c>
       <c r="AH7">
-        <v>0.002962021387449839</v>
+        <v>0.001740169961459145</v>
       </c>
       <c r="AI7">
-        <v>0.01418439716312057</v>
+        <v>0.008536339581179745</v>
       </c>
       <c r="AJ7">
-        <v>-0.04954427913952931</v>
+        <v>-0.01953079528196409</v>
       </c>
       <c r="AK7">
-        <v>-0.2963931679620235</v>
+        <v>-0.1045042043586271</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PT Bank Panin Dubai Syariah Tbk (IDX:PNBS)</t>
+          <t>PT Bank Jago Tbk (IDX:ARTO)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1319,8 +1319,29 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
+      <c r="D8">
+        <v>1.094</v>
+      </c>
+      <c r="F8">
+        <v>1.461</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
       <c r="K8">
-        <v>-42.8</v>
+        <v>1.66</v>
+      </c>
+      <c r="L8">
+        <v>0.0203680981595092</v>
       </c>
       <c r="M8">
         <v>-0</v>
@@ -1329,7 +1350,7 @@
         <v>-0</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P8">
         <v>-0</v>
@@ -1338,61 +1359,61 @@
         <v>-0</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
       <c r="U8">
-        <v>66.3</v>
+        <v>62.8</v>
       </c>
       <c r="V8">
-        <v>0.4236421725239616</v>
+        <v>0.02404379953290708</v>
       </c>
       <c r="W8">
-        <v>-0.1959706959706959</v>
+        <v>0.003049788719456182</v>
       </c>
       <c r="X8">
-        <v>0.07972753914207885</v>
+        <v>0.06790035944476672</v>
       </c>
       <c r="Y8">
-        <v>-0.2756982351127748</v>
+        <v>-0.06485057072531053</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>0.1599670252021669</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.07968678191995188</v>
+        <v>0.06788651978327669</v>
       </c>
       <c r="AC8">
-        <v>-0.07968678191995188</v>
+        <v>-0.06788651978327669</v>
       </c>
       <c r="AD8">
-        <v>0.644</v>
+        <v>3.63</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>0.644</v>
+        <v>3.63</v>
       </c>
       <c r="AG8">
-        <v>-65.65599999999999</v>
+        <v>-59.16999999999999</v>
       </c>
       <c r="AH8">
-        <v>0.004098152013439902</v>
+        <v>0.001387864027558468</v>
       </c>
       <c r="AI8">
-        <v>0.004119121936243157</v>
+        <v>0.006693341692327549</v>
       </c>
       <c r="AJ8">
-        <v>-0.7227334771696533</v>
+        <v>-0.02317910629012861</v>
       </c>
       <c r="AK8">
-        <v>-0.7291546355115276</v>
+        <v>-0.1233916543281963</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1409,7 +1430,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PT Bank Maspion Indonesia Tbk (IDX:BMAS)</t>
+          <t>PT Bank Aladin Syariah Tbk (IDX:BANK)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1418,10 +1439,7 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.09210000000000002</v>
-      </c>
-      <c r="E9">
-        <v>0.116</v>
+        <v>-0.135</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1436,10 +1454,10 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>7.84</v>
+        <v>-17.1</v>
       </c>
       <c r="L9">
-        <v>0.2861313868613139</v>
+        <v>-1.613207547169812</v>
       </c>
       <c r="M9">
         <v>-0</v>
@@ -1448,7 +1466,7 @@
         <v>-0</v>
       </c>
       <c r="O9">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P9">
         <v>-0</v>
@@ -1457,61 +1475,61 @@
         <v>-0</v>
       </c>
       <c r="R9">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
       <c r="U9">
-        <v>51.5</v>
+        <v>109.1</v>
       </c>
       <c r="V9">
-        <v>0.1661290322580645</v>
+        <v>0.09257530759439965</v>
       </c>
       <c r="W9">
-        <v>0.08634361233480177</v>
+        <v>-0.1291540785498489</v>
       </c>
       <c r="X9">
-        <v>0.07966797259519545</v>
+        <v>0.06790982774192329</v>
       </c>
       <c r="Y9">
-        <v>0.006675639739606318</v>
+        <v>-0.1970639062917722</v>
       </c>
       <c r="Z9">
-        <v>3.30120481927711</v>
+        <v>0.103850298814539</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.07983883487833272</v>
+        <v>0.06788806425796577</v>
       </c>
       <c r="AC9">
-        <v>-0.07983883487833272</v>
+        <v>-0.06788806425796577</v>
       </c>
       <c r="AD9">
-        <v>0.743</v>
+        <v>2.13</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>0.743</v>
+        <v>2.13</v>
       </c>
       <c r="AG9">
-        <v>-50.757</v>
+        <v>-106.97</v>
       </c>
       <c r="AH9">
-        <v>0.002391043402425799</v>
+        <v>0.001804121528336566</v>
       </c>
       <c r="AI9">
-        <v>0.007951371424290744</v>
+        <v>0.01059016556456023</v>
       </c>
       <c r="AJ9">
-        <v>-0.1957892787847695</v>
+        <v>-0.09982921616753614</v>
       </c>
       <c r="AK9">
-        <v>-1.210142336027466</v>
+        <v>-1.162338367923503</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1528,7 +1546,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PT Bank Syariah Indonesia Tbk (IDX:BRIS)</t>
+          <t>PT Bank Amar Indonesia Tbk (IDX:AMAR)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1537,10 +1555,10 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.6409999999999999</v>
+        <v>0.357</v>
       </c>
       <c r="E10">
-        <v>0.882</v>
+        <v>0.612</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1555,85 +1573,85 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>261.1</v>
+        <v>11.6</v>
       </c>
       <c r="L10">
-        <v>0.2617019144031272</v>
+        <v>0.2892768079800498</v>
       </c>
       <c r="M10">
-        <v>49.7</v>
+        <v>0.113</v>
       </c>
       <c r="N10">
-        <v>0.01463658852632819</v>
+        <v>0.000298546895640687</v>
       </c>
       <c r="O10">
-        <v>0.1903485254691689</v>
+        <v>0.009741379310344828</v>
       </c>
       <c r="P10">
-        <v>49.7</v>
+        <v>-0</v>
       </c>
       <c r="Q10">
-        <v>0.01463658852632819</v>
+        <v>-0</v>
       </c>
       <c r="R10">
-        <v>0.1903485254691689</v>
+        <v>-0</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>0.113</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U10">
-        <v>533.8</v>
+        <v>50.5</v>
       </c>
       <c r="V10">
-        <v>0.1572034397455531</v>
+        <v>0.1334214002642008</v>
       </c>
       <c r="W10">
-        <v>0.1546251332464764</v>
+        <v>0.09423233143785541</v>
       </c>
       <c r="X10">
-        <v>0.08022603565671205</v>
+        <v>0.0679122182636361</v>
       </c>
       <c r="Y10">
-        <v>0.07439909758976435</v>
+        <v>0.02632011317421931</v>
       </c>
       <c r="Z10">
-        <v>1.233403387316109</v>
+        <v>0.5150865114128271</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.07997773805004098</v>
+        <v>0.0678891830928685</v>
       </c>
       <c r="AC10">
-        <v>-0.07997773805004098</v>
+        <v>-0.0678891830928685</v>
       </c>
       <c r="AD10">
-        <v>62.8</v>
+        <v>0.724</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>62.8</v>
+        <v>0.724</v>
       </c>
       <c r="AG10">
-        <v>-470.9999999999999</v>
+        <v>-49.776</v>
       </c>
       <c r="AH10">
-        <v>0.01815868609761739</v>
+        <v>0.001909161867392359</v>
       </c>
       <c r="AI10">
-        <v>0.03355597114613946</v>
+        <v>0.003346831604445184</v>
       </c>
       <c r="AJ10">
-        <v>-0.1610476646378992</v>
+        <v>-0.1514218615008335</v>
       </c>
       <c r="AK10">
-        <v>-0.3520968827091275</v>
+        <v>-0.3001736781165574</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1650,7 +1668,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PT Bank Mestika Dharma Tbk (IDX:BBMD)</t>
+          <t>PT Bank Multiarta Sentosa Tbk (IDX:MASB)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1658,12 +1676,6 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D11">
-        <v>0.0919</v>
-      </c>
-      <c r="E11">
-        <v>0.139</v>
-      </c>
       <c r="G11">
         <v>0</v>
       </c>
@@ -1677,85 +1689,82 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>36.9</v>
+        <v>16.3</v>
       </c>
       <c r="L11">
-        <v>0.5</v>
+        <v>0.3202357563850688</v>
       </c>
       <c r="M11">
-        <v>16.9</v>
+        <v>-0</v>
       </c>
       <c r="N11">
-        <v>0.03092972181551976</v>
+        <v>-0</v>
       </c>
       <c r="O11">
-        <v>0.4579945799457995</v>
+        <v>-0</v>
       </c>
       <c r="P11">
-        <v>16.9</v>
+        <v>-0</v>
       </c>
       <c r="Q11">
-        <v>0.03092972181551976</v>
+        <v>-0</v>
       </c>
       <c r="R11">
-        <v>0.4579945799457995</v>
+        <v>-0</v>
       </c>
       <c r="S11">
         <v>0</v>
       </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
       <c r="U11">
-        <v>53.9</v>
+        <v>177.4</v>
       </c>
       <c r="V11">
-        <v>0.09864568081991215</v>
+        <v>0.5448402948402948</v>
       </c>
       <c r="W11">
-        <v>0.1319270647121916</v>
+        <v>0.08089330024813896</v>
       </c>
       <c r="X11">
-        <v>0.08339801606205824</v>
+        <v>0.06800115737794181</v>
       </c>
       <c r="Y11">
-        <v>0.04852904865013338</v>
+        <v>0.01289214287019715</v>
       </c>
       <c r="Z11">
-        <v>0.2691466083150985</v>
+        <v>0.4656907593778591</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.08204878885722168</v>
+        <v>0.06790434212384008</v>
       </c>
       <c r="AC11">
-        <v>-0.08204878885722168</v>
+        <v>-0.06790434212384008</v>
       </c>
       <c r="AD11">
-        <v>60.1</v>
+        <v>1.9</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>60.1</v>
+        <v>1.9</v>
       </c>
       <c r="AG11">
-        <v>6.200000000000003</v>
+        <v>-175.5</v>
       </c>
       <c r="AH11">
-        <v>0.09909315746084089</v>
+        <v>0.005801526717557252</v>
       </c>
       <c r="AI11">
-        <v>0.1767127315495443</v>
+        <v>0.008030431107354184</v>
       </c>
       <c r="AJ11">
-        <v>0.01121968874411872</v>
+        <v>-1.169220519653564</v>
       </c>
       <c r="AK11">
-        <v>0.02166317260656885</v>
+        <v>-2.964527027027028</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1772,7 +1781,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>P.T. Bank Pan Indonesia Tbk (IDX:PNBN)</t>
+          <t>PT Bank Panin Dubai Syariah Tbk (IDX:PNBS)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1780,12 +1789,6 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D12">
-        <v>-0.0139</v>
-      </c>
-      <c r="E12">
-        <v>-0.04480000000000001</v>
-      </c>
       <c r="G12">
         <v>0</v>
       </c>
@@ -1799,85 +1802,82 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>145.9</v>
+        <v>19.2</v>
       </c>
       <c r="L12">
-        <v>0.2822050290135397</v>
+        <v>0.5378151260504201</v>
       </c>
       <c r="M12">
-        <v>31.6</v>
+        <v>-0</v>
       </c>
       <c r="N12">
-        <v>0.01331367179271119</v>
+        <v>-0</v>
       </c>
       <c r="O12">
-        <v>0.2165867032213845</v>
+        <v>-0</v>
       </c>
       <c r="P12">
-        <v>31.6</v>
+        <v>-0</v>
       </c>
       <c r="Q12">
-        <v>0.01331367179271119</v>
+        <v>-0</v>
       </c>
       <c r="R12">
-        <v>0.2165867032213845</v>
+        <v>-0</v>
       </c>
       <c r="S12">
         <v>0</v>
       </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
       <c r="U12">
-        <v>615.7</v>
+        <v>47.8</v>
       </c>
       <c r="V12">
-        <v>0.2594059405940594</v>
+        <v>0.3509544787077827</v>
       </c>
       <c r="W12">
-        <v>0.04656729756471227</v>
+        <v>0.1233140655105973</v>
       </c>
       <c r="X12">
-        <v>0.08872234672350973</v>
+        <v>0.06804697442398773</v>
       </c>
       <c r="Y12">
-        <v>-0.04215504915879746</v>
+        <v>0.05526709108660957</v>
       </c>
       <c r="Z12">
-        <v>0.1566429328889562</v>
+        <v>0.3964728355026432</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.0840977594818485</v>
+        <v>0.06795187444586852</v>
       </c>
       <c r="AC12">
-        <v>-0.0840977594818485</v>
+        <v>-0.06795187444586852</v>
       </c>
       <c r="AD12">
-        <v>625.6</v>
+        <v>1.07</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>625.6</v>
+        <v>1.07</v>
       </c>
       <c r="AG12">
-        <v>9.899999999999977</v>
+        <v>-46.73</v>
       </c>
       <c r="AH12">
-        <v>0.2085959121069654</v>
+        <v>0.007794856851460626</v>
       </c>
       <c r="AI12">
-        <v>0.1618168179819456</v>
+        <v>0.006022401080655148</v>
       </c>
       <c r="AJ12">
-        <v>0.004153729965595358</v>
+        <v>-0.5222979769755225</v>
       </c>
       <c r="AK12">
-        <v>0.003045778981048479</v>
+        <v>-0.3598213598213598</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PT Bank Rakyat Indonesia (Persero) Tbk (IDX:BBRI)</t>
+          <t>PT Bank Mestika Dharma Tbk (IDX:BBMD)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1903,13 +1903,10 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.141</v>
+        <v>0.0735</v>
       </c>
       <c r="E13">
-        <v>0.14</v>
-      </c>
-      <c r="F13">
-        <v>0.226</v>
+        <v>0.104</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1924,85 +1921,85 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>3504.6</v>
+        <v>27.8</v>
       </c>
       <c r="L13">
-        <v>0.41343919213845</v>
+        <v>0.4296754250386399</v>
       </c>
       <c r="M13">
-        <v>1815.4</v>
+        <v>8.92</v>
       </c>
       <c r="N13">
-        <v>0.0379582739168071</v>
+        <v>0.01703915950334288</v>
       </c>
       <c r="O13">
-        <v>0.5180049078354163</v>
+        <v>0.320863309352518</v>
       </c>
       <c r="P13">
-        <v>1734.1</v>
+        <v>8.92</v>
       </c>
       <c r="Q13">
-        <v>0.03625836884385546</v>
+        <v>0.01703915950334288</v>
       </c>
       <c r="R13">
-        <v>0.4948068253152999</v>
+        <v>0.320863309352518</v>
       </c>
       <c r="S13">
-        <v>81.29999999999995</v>
+        <v>0</v>
       </c>
       <c r="T13">
-        <v>0.0447835187837391</v>
+        <v>0</v>
       </c>
       <c r="U13">
-        <v>4910.1</v>
+        <v>32.1</v>
       </c>
       <c r="V13">
-        <v>0.1026654846088546</v>
+        <v>0.06131805157593123</v>
       </c>
       <c r="W13">
-        <v>0.1805471124620061</v>
+        <v>0.09928571428571428</v>
       </c>
       <c r="X13">
-        <v>0.08706410166428628</v>
+        <v>0.06842756927340142</v>
       </c>
       <c r="Y13">
-        <v>0.0934830107977198</v>
+        <v>0.03085814501231286</v>
       </c>
       <c r="Z13">
-        <v>0.414494369385889</v>
+        <v>0.2260656883298393</v>
       </c>
       <c r="AA13">
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.08431406207574342</v>
+        <v>0.0681750735528826</v>
       </c>
       <c r="AC13">
-        <v>-0.08431406207574342</v>
+        <v>-0.0681750735528826</v>
       </c>
       <c r="AD13">
-        <v>10318.2</v>
+        <v>12.9</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>10318.2</v>
+        <v>12.9</v>
       </c>
       <c r="AG13">
-        <v>5408.1</v>
+        <v>-19.2</v>
       </c>
       <c r="AH13">
-        <v>0.1774581902986359</v>
+        <v>0.02404921700223714</v>
       </c>
       <c r="AI13">
-        <v>0.3434717335366118</v>
+        <v>0.04023705552089832</v>
       </c>
       <c r="AJ13">
-        <v>0.1015905158891918</v>
+        <v>-0.0380725758477097</v>
       </c>
       <c r="AK13">
-        <v>0.2151980836264663</v>
+        <v>-0.06655112651646448</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2019,7 +2016,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PT Bank Mega Tbk (IDX:MEGA)</t>
+          <t>PT Bank Syariah Indonesia Tbk (IDX:BRIS)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2028,10 +2025,13 @@
         </is>
       </c>
       <c r="D14">
-        <v>0.134</v>
+        <v>0.655</v>
       </c>
       <c r="E14">
-        <v>0.322</v>
+        <v>1.112</v>
+      </c>
+      <c r="F14">
+        <v>0.196</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2046,28 +2046,28 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>270.5</v>
+        <v>339.7</v>
       </c>
       <c r="L14">
-        <v>0.4961482024944974</v>
+        <v>0.3085376930063579</v>
       </c>
       <c r="M14">
-        <v>183.9</v>
+        <v>27.5</v>
       </c>
       <c r="N14">
-        <v>0.0463960441002094</v>
+        <v>0.005324298160696999</v>
       </c>
       <c r="O14">
-        <v>0.6798521256931608</v>
+        <v>0.08095378274948484</v>
       </c>
       <c r="P14">
-        <v>183.9</v>
+        <v>27.5</v>
       </c>
       <c r="Q14">
-        <v>0.0463960441002094</v>
+        <v>0.005324298160696999</v>
       </c>
       <c r="R14">
-        <v>0.6798521256931608</v>
+        <v>0.08095378274948484</v>
       </c>
       <c r="S14">
         <v>0</v>
@@ -2076,55 +2076,55 @@
         <v>0</v>
       </c>
       <c r="U14">
-        <v>149.8</v>
+        <v>723.1</v>
       </c>
       <c r="V14">
-        <v>0.03779297121376492</v>
+        <v>0.14</v>
       </c>
       <c r="W14">
-        <v>0.2110972373965975</v>
+        <v>0.1878144523691049</v>
       </c>
       <c r="X14">
-        <v>0.08950215305168932</v>
+        <v>0.07103877599054217</v>
       </c>
       <c r="Y14">
-        <v>0.1215950843449081</v>
+        <v>0.1167756763785627</v>
       </c>
       <c r="Z14">
-        <v>0.3396038370499564</v>
+        <v>0.8230544965238843</v>
       </c>
       <c r="AA14">
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.08511570165022238</v>
+        <v>0.06861928395501266</v>
       </c>
       <c r="AC14">
-        <v>-0.08511570165022238</v>
+        <v>-0.06861928395501266</v>
       </c>
       <c r="AD14">
-        <v>1133.9</v>
+        <v>722.1</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>1133.9</v>
+        <v>722.1</v>
       </c>
       <c r="AG14">
-        <v>984.1000000000001</v>
+        <v>-1</v>
       </c>
       <c r="AH14">
-        <v>0.2224380100439423</v>
+        <v>0.1226580149819096</v>
       </c>
       <c r="AI14">
-        <v>0.487908777969019</v>
+        <v>0.2310646059326102</v>
       </c>
       <c r="AJ14">
-        <v>0.1988964792433001</v>
+        <v>-0.0001936483346243222</v>
       </c>
       <c r="AK14">
-        <v>0.4526262533345599</v>
+        <v>-0.0004163197335553705</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PT Bank Mandiri (Persero) Tbk (IDX:BMRI)</t>
+          <t>PT Bank Rakyat Indonesia (Persero) Tbk (IDX:BBRI)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2150,13 +2150,13 @@
         </is>
       </c>
       <c r="D15">
-        <v>0.129</v>
+        <v>0.13</v>
       </c>
       <c r="E15">
-        <v>0.185</v>
+        <v>0.119</v>
       </c>
       <c r="F15">
-        <v>0.269</v>
+        <v>0.131</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2171,85 +2171,85 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>2590.8</v>
+        <v>3620.1</v>
       </c>
       <c r="L15">
-        <v>0.3851116330231591</v>
+        <v>0.3902441653640921</v>
       </c>
       <c r="M15">
-        <v>1104.3</v>
+        <v>2942.7</v>
       </c>
       <c r="N15">
-        <v>0.03725369146535235</v>
+        <v>0.0524202527045587</v>
       </c>
       <c r="O15">
-        <v>0.4262389995368225</v>
+        <v>0.8128780972901302</v>
       </c>
       <c r="P15">
-        <v>1104.3</v>
+        <v>2811.4</v>
       </c>
       <c r="Q15">
-        <v>0.03725369146535235</v>
+        <v>0.05008131935079903</v>
       </c>
       <c r="R15">
-        <v>0.4262389995368225</v>
+        <v>0.7766083809839508</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>131.3000000000002</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>0.04461888741631841</v>
       </c>
       <c r="U15">
-        <v>3508.1</v>
+        <v>4041.6</v>
       </c>
       <c r="V15">
-        <v>0.118346169545959</v>
+        <v>0.07199568196919306</v>
       </c>
       <c r="W15">
-        <v>0.1886770467687199</v>
+        <v>0.1858749229821318</v>
       </c>
       <c r="X15">
-        <v>0.09069443576843639</v>
+        <v>0.0718918284932554</v>
       </c>
       <c r="Y15">
-        <v>0.09798261100028349</v>
+        <v>0.1139830944888764</v>
       </c>
       <c r="Z15">
-        <v>0.3854779654024444</v>
+        <v>0.3727882463098927</v>
       </c>
       <c r="AA15">
         <v>0</v>
       </c>
       <c r="AB15">
-        <v>0.08605246223098816</v>
+        <v>0.06994609976388047</v>
       </c>
       <c r="AC15">
-        <v>-0.08605246223098816</v>
+        <v>-0.06994609976388047</v>
       </c>
       <c r="AD15">
-        <v>9499.4</v>
+        <v>9960.299999999999</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>9499.4</v>
+        <v>9960.299999999999</v>
       </c>
       <c r="AG15">
-        <v>5991.299999999999</v>
+        <v>5918.699999999999</v>
       </c>
       <c r="AH15">
-        <v>0.2426900958303208</v>
+        <v>0.1506921645460459</v>
       </c>
       <c r="AI15">
-        <v>0.3846783076324997</v>
+        <v>0.3309410603749888</v>
       </c>
       <c r="AJ15">
-        <v>0.1681343660548914</v>
+        <v>0.09537767865487934</v>
       </c>
       <c r="AK15">
-        <v>0.2827912377338185</v>
+        <v>0.2271591576377935</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PT Bank OCBC NISP Tbk (IDX:NISP)</t>
+          <t>PT Bank Mega Tbk (IDX:MEGA)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="D16">
-        <v>0.0619</v>
+        <v>0.11</v>
       </c>
       <c r="E16">
-        <v>0.0762</v>
+        <v>0.241</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2293,28 +2293,28 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>199.1</v>
+        <v>271.9</v>
       </c>
       <c r="L16">
-        <v>0.3731958762886598</v>
+        <v>0.5000919624793083</v>
       </c>
       <c r="M16">
-        <v>33.1</v>
+        <v>183.4</v>
       </c>
       <c r="N16">
-        <v>0.03025594149908592</v>
+        <v>0.0475968026575314</v>
       </c>
       <c r="O16">
-        <v>0.1662481165243596</v>
+        <v>0.6745126884884149</v>
       </c>
       <c r="P16">
-        <v>33.1</v>
+        <v>183.4</v>
       </c>
       <c r="Q16">
-        <v>0.03025594149908592</v>
+        <v>0.0475968026575314</v>
       </c>
       <c r="R16">
-        <v>0.1662481165243596</v>
+        <v>0.6745126884884149</v>
       </c>
       <c r="S16">
         <v>0</v>
@@ -2323,55 +2323,55 @@
         <v>0</v>
       </c>
       <c r="U16">
-        <v>364</v>
+        <v>111.9</v>
       </c>
       <c r="V16">
-        <v>0.3327239488117002</v>
+        <v>0.02904079725942075</v>
       </c>
       <c r="W16">
-        <v>0.08938672892161263</v>
+        <v>0.2284681959499202</v>
       </c>
       <c r="X16">
-        <v>0.11176766052565</v>
+        <v>0.0728093749284487</v>
       </c>
       <c r="Y16">
-        <v>-0.02238093160403741</v>
+        <v>0.1556588210214715</v>
       </c>
       <c r="Z16">
-        <v>0.2725693557451592</v>
+        <v>0.2500689908932021</v>
       </c>
       <c r="AA16">
         <v>0</v>
       </c>
       <c r="AB16">
-        <v>0.08684926274141132</v>
+        <v>0.07014699237295879</v>
       </c>
       <c r="AC16">
-        <v>-0.08684926274141132</v>
+        <v>-0.07014699237295879</v>
       </c>
       <c r="AD16">
-        <v>1015.6</v>
+        <v>839.6</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>1015.6</v>
+        <v>839.6</v>
       </c>
       <c r="AG16">
-        <v>651.6</v>
+        <v>727.7</v>
       </c>
       <c r="AH16">
-        <v>0.481418278346606</v>
+        <v>0.1789123764064098</v>
       </c>
       <c r="AI16">
-        <v>0.317931379914851</v>
+        <v>0.385526678299201</v>
       </c>
       <c r="AJ16">
-        <v>0.3732813932172319</v>
+        <v>0.1588552467855662</v>
       </c>
       <c r="AK16">
-        <v>0.2302148106274731</v>
+        <v>0.3522435742291495</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PT Bank Pembangunan Daerah Jawa Barat dan Banten Tbk (IDX:BJBR)</t>
+          <t>PT Bank OCBC NISP Tbk (IDX:NISP)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2397,10 +2397,10 @@
         </is>
       </c>
       <c r="D17">
-        <v>0.101</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="E17">
-        <v>0.182</v>
+        <v>0.0857</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2415,28 +2415,28 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>160.6</v>
+        <v>247.7</v>
       </c>
       <c r="L17">
-        <v>0.2520006276478896</v>
+        <v>0.3693707127945123</v>
       </c>
       <c r="M17">
-        <v>68.5</v>
+        <v>86</v>
       </c>
       <c r="N17">
-        <v>0.07563210776195207</v>
+        <v>0.04886641286436729</v>
       </c>
       <c r="O17">
-        <v>0.4265255292652553</v>
+        <v>0.3471941865159467</v>
       </c>
       <c r="P17">
-        <v>68.5</v>
+        <v>86</v>
       </c>
       <c r="Q17">
-        <v>0.07563210776195207</v>
+        <v>0.04886641286436729</v>
       </c>
       <c r="R17">
-        <v>0.4265255292652553</v>
+        <v>0.3471941865159467</v>
       </c>
       <c r="S17">
         <v>0</v>
@@ -2445,55 +2445,55 @@
         <v>0</v>
       </c>
       <c r="U17">
-        <v>643.6</v>
+        <v>205.9</v>
       </c>
       <c r="V17">
-        <v>0.7106105774539031</v>
+        <v>0.1169952838229445</v>
       </c>
       <c r="W17">
-        <v>0.185686206497861</v>
+        <v>0.1136864328988434</v>
       </c>
       <c r="X17">
-        <v>0.1473689809824843</v>
+        <v>0.08244654694726949</v>
       </c>
       <c r="Y17">
-        <v>0.0383172255153767</v>
+        <v>0.03123988595157388</v>
       </c>
       <c r="Z17">
-        <v>0.6238253719655442</v>
+        <v>0.2369276427360091</v>
       </c>
       <c r="AA17">
         <v>0</v>
       </c>
       <c r="AB17">
-        <v>0.08956846807745322</v>
+        <v>0.07026306882505411</v>
       </c>
       <c r="AC17">
-        <v>-0.08956846807745322</v>
+        <v>-0.07026306882505411</v>
       </c>
       <c r="AD17">
-        <v>1770.9</v>
+        <v>1131.5</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>1770.9</v>
+        <v>1131.5</v>
       </c>
       <c r="AG17">
-        <v>1127.3</v>
+        <v>925.6</v>
       </c>
       <c r="AH17">
-        <v>0.6616229544945079</v>
+        <v>0.3913329183094694</v>
       </c>
       <c r="AI17">
-        <v>0.6589150171156422</v>
+        <v>0.3272974458361054</v>
       </c>
       <c r="AJ17">
-        <v>0.5545007378258732</v>
+        <v>0.3446657978030162</v>
       </c>
       <c r="AK17">
-        <v>0.5515166340508807</v>
+        <v>0.2846948818897638</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -2510,7 +2510,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PT Bank BTPN Tbk (IDX:BTPN)</t>
+          <t>PT Bank Pembangunan Daerah Jawa Timur Tbk (IDX:BJTM)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2519,10 +2519,10 @@
         </is>
       </c>
       <c r="D18">
-        <v>0.0547</v>
+        <v>0.0528</v>
       </c>
       <c r="E18">
-        <v>0.12</v>
+        <v>0.0354</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -2531,100 +2531,97 @@
         <v>0</v>
       </c>
       <c r="I18">
-        <v>-0.006756577586524283</v>
+        <v>0</v>
       </c>
       <c r="J18">
-        <v>-0.005237866340802041</v>
+        <v>0</v>
       </c>
       <c r="K18">
-        <v>199.4</v>
+        <v>92.7</v>
       </c>
       <c r="L18">
-        <v>0.2590283190439076</v>
+        <v>0.2894161723384327</v>
       </c>
       <c r="M18">
-        <v>-0</v>
+        <v>51.5</v>
       </c>
       <c r="N18">
-        <v>-0</v>
+        <v>0.08442622950819673</v>
       </c>
       <c r="O18">
-        <v>-0</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="P18">
-        <v>-0</v>
+        <v>51.5</v>
       </c>
       <c r="Q18">
-        <v>-0</v>
+        <v>0.08442622950819673</v>
       </c>
       <c r="R18">
-        <v>-0</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="S18">
         <v>0</v>
       </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
       <c r="U18">
-        <v>959.3</v>
+        <v>422.6</v>
       </c>
       <c r="V18">
-        <v>0.7020638173302107</v>
+        <v>0.6927868852459017</v>
       </c>
       <c r="W18">
-        <v>0.08556470992104359</v>
+        <v>0.1294150495602401</v>
       </c>
       <c r="X18">
-        <v>0.1713882902887746</v>
+        <v>0.08807817776894294</v>
       </c>
       <c r="Y18">
-        <v>-0.08582358036773105</v>
+        <v>0.04133687179129719</v>
       </c>
       <c r="Z18">
-        <v>0.189436255433076</v>
+        <v>0.804976124654436</v>
       </c>
       <c r="AA18">
-        <v>-0.0009922417860604867</v>
+        <v>0</v>
       </c>
       <c r="AB18">
-        <v>0.0905381915820159</v>
+        <v>0.0707521110880296</v>
       </c>
       <c r="AC18">
-        <v>-0.09153043336807638</v>
+        <v>-0.0707521110880296</v>
       </c>
       <c r="AD18">
-        <v>3591</v>
+        <v>543.7</v>
       </c>
       <c r="AE18">
-        <v>27.41606713053196</v>
+        <v>0</v>
       </c>
       <c r="AF18">
-        <v>3618.416067130532</v>
+        <v>543.7</v>
       </c>
       <c r="AG18">
-        <v>2659.116067130532</v>
+        <v>121.1</v>
       </c>
       <c r="AH18">
-        <v>0.7258875790804139</v>
+        <v>0.4712663604056514</v>
       </c>
       <c r="AI18">
-        <v>0.5880623780948697</v>
+        <v>0.4172678434382195</v>
       </c>
       <c r="AJ18">
-        <v>0.6605652599036831</v>
+        <v>0.1656408152099576</v>
       </c>
       <c r="AK18">
-        <v>0.5119773270291481</v>
+        <v>0.1375511131303953</v>
       </c>
       <c r="AL18">
         <v>0</v>
       </c>
       <c r="AM18">
         <v>0</v>
-      </c>
-      <c r="AN18">
-        <v>12734.04255319149</v>
-      </c>
-      <c r="AP18">
-        <v>9429.489599753662</v>
       </c>
     </row>
     <row r="19">
@@ -2635,7 +2632,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PT Bank Nationalnobu Tbk (IDX:NOBU)</t>
+          <t>P.T. Bank Pan Indonesia Tbk (IDX:PNBN)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2644,10 +2641,10 @@
         </is>
       </c>
       <c r="D19">
-        <v>0.133</v>
+        <v>0.0421</v>
       </c>
       <c r="E19">
-        <v>0.25</v>
+        <v>0.0464</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2662,82 +2659,85 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>5.84</v>
+        <v>196.6</v>
       </c>
       <c r="L19">
-        <v>0.1361305361305361</v>
+        <v>0.3173014848289218</v>
       </c>
       <c r="M19">
-        <v>-0</v>
+        <v>12.5</v>
       </c>
       <c r="N19">
-        <v>-0</v>
+        <v>0.006599788806758183</v>
       </c>
       <c r="O19">
-        <v>-0</v>
+        <v>0.06358087487283826</v>
       </c>
       <c r="P19">
-        <v>-0</v>
+        <v>12.5</v>
       </c>
       <c r="Q19">
-        <v>-0</v>
+        <v>0.006599788806758183</v>
       </c>
       <c r="R19">
-        <v>-0</v>
+        <v>0.06358087487283826</v>
       </c>
       <c r="S19">
         <v>0</v>
       </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
       <c r="U19">
-        <v>112.3</v>
+        <v>561.3</v>
       </c>
       <c r="V19">
-        <v>0.6932098765432099</v>
+        <v>0.2963569165786695</v>
       </c>
       <c r="W19">
-        <v>0.05372585096596136</v>
+        <v>0.06482244716278149</v>
       </c>
       <c r="X19">
-        <v>0.1294242623686088</v>
+        <v>0.07469968925221449</v>
       </c>
       <c r="Y19">
-        <v>-0.07569841140264741</v>
+        <v>-0.009877242089432997</v>
       </c>
       <c r="Z19">
-        <v>0.3672945205479452</v>
+        <v>0.2036282371499934</v>
       </c>
       <c r="AA19">
         <v>0</v>
       </c>
       <c r="AB19">
-        <v>0.09234427535143941</v>
+        <v>0.07081683928449406</v>
       </c>
       <c r="AC19">
-        <v>-0.09234427535143941</v>
+        <v>-0.07081683928449406</v>
       </c>
       <c r="AD19">
-        <v>232.9</v>
+        <v>570.6</v>
       </c>
       <c r="AE19">
         <v>0</v>
       </c>
       <c r="AF19">
-        <v>232.9</v>
+        <v>570.6</v>
       </c>
       <c r="AG19">
-        <v>120.6</v>
+        <v>9.300000000000068</v>
       </c>
       <c r="AH19">
-        <v>0.5897695619144088</v>
+        <v>0.2315182991154751</v>
       </c>
       <c r="AI19">
-        <v>0.6656187482137754</v>
+        <v>0.1418203509469603</v>
       </c>
       <c r="AJ19">
-        <v>0.4267515923566879</v>
+        <v>0.004886250197026253</v>
       </c>
       <c r="AK19">
-        <v>0.5075757575757576</v>
+        <v>0.002686230900320634</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -2754,93 +2754,706 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>PT Bank Capital Indonesia Tbk (IDX:BACA)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D20">
+        <v>0.00186</v>
+      </c>
+      <c r="E20">
+        <v>-0.123</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>4.16</v>
+      </c>
+      <c r="L20">
+        <v>0.1212827988338193</v>
+      </c>
+      <c r="M20">
+        <v>-0</v>
+      </c>
+      <c r="N20">
+        <v>-0</v>
+      </c>
+      <c r="O20">
+        <v>-0</v>
+      </c>
+      <c r="P20">
+        <v>-0</v>
+      </c>
+      <c r="Q20">
+        <v>-0</v>
+      </c>
+      <c r="R20">
+        <v>-0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>51.6</v>
+      </c>
+      <c r="V20">
+        <v>0.3044247787610619</v>
+      </c>
+      <c r="W20">
+        <v>0.02952448545067424</v>
+      </c>
+      <c r="X20">
+        <v>0.07684469047368864</v>
+      </c>
+      <c r="Y20">
+        <v>-0.0473202050230144</v>
+      </c>
+      <c r="Z20">
+        <v>0.1233812949640288</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>0.07088961777565167</v>
+      </c>
+      <c r="AC20">
+        <v>-0.07088961777565167</v>
+      </c>
+      <c r="AD20">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="AG20">
+        <v>15.49999999999999</v>
+      </c>
+      <c r="AH20">
+        <v>0.2836010143702451</v>
+      </c>
+      <c r="AI20">
+        <v>0.2359353023909986</v>
+      </c>
+      <c r="AJ20">
+        <v>0.08378378378378375</v>
+      </c>
+      <c r="AK20">
+        <v>0.06658075601374568</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>PT Bank Mandiri (Persero) Tbk (IDX:BMRI)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D21">
+        <v>0.125</v>
+      </c>
+      <c r="E21">
+        <v>0.159</v>
+      </c>
+      <c r="F21">
+        <v>0.203</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>3204.8</v>
+      </c>
+      <c r="L21">
+        <v>0.407413999135542</v>
+      </c>
+      <c r="M21">
+        <v>1596.7</v>
+      </c>
+      <c r="N21">
+        <v>0.04394228361170509</v>
+      </c>
+      <c r="O21">
+        <v>0.4982214178731902</v>
+      </c>
+      <c r="P21">
+        <v>1596.7</v>
+      </c>
+      <c r="Q21">
+        <v>0.04394228361170509</v>
+      </c>
+      <c r="R21">
+        <v>0.4982214178731902</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>3726.1</v>
+      </c>
+      <c r="V21">
+        <v>0.1025448380820281</v>
+      </c>
+      <c r="W21">
+        <v>0.2300959929925833</v>
+      </c>
+      <c r="X21">
+        <v>0.0748942300204033</v>
+      </c>
+      <c r="Y21">
+        <v>0.1552017629721801</v>
+      </c>
+      <c r="Z21">
+        <v>0.3959290708033643</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0.07112965732437088</v>
+      </c>
+      <c r="AC21">
+        <v>-0.07112965732437088</v>
+      </c>
+      <c r="AD21">
+        <v>11258.7</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>11258.7</v>
+      </c>
+      <c r="AG21">
+        <v>7532.6</v>
+      </c>
+      <c r="AH21">
+        <v>0.2365521588402143</v>
+      </c>
+      <c r="AI21">
+        <v>0.3933788717877046</v>
+      </c>
+      <c r="AJ21">
+        <v>0.1717070635461568</v>
+      </c>
+      <c r="AK21">
+        <v>0.3025821068192043</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>PT Bank KB Bukopin Tbk (IDX:BBKP)</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="K20">
-        <v>-386.3</v>
-      </c>
-      <c r="M20">
-        <v>-0</v>
-      </c>
-      <c r="N20">
-        <v>-0</v>
-      </c>
-      <c r="O20">
-        <v>0</v>
-      </c>
-      <c r="P20">
-        <v>-0</v>
-      </c>
-      <c r="Q20">
-        <v>-0</v>
-      </c>
-      <c r="R20">
-        <v>0</v>
-      </c>
-      <c r="S20">
-        <v>0</v>
-      </c>
-      <c r="U20">
-        <v>1091.6</v>
-      </c>
-      <c r="V20">
-        <v>2.462996389891697</v>
-      </c>
-      <c r="W20">
-        <v>-0.6530853761622992</v>
-      </c>
-      <c r="X20">
-        <v>0.196390966859342</v>
-      </c>
-      <c r="Y20">
-        <v>-0.8494763430216412</v>
-      </c>
-      <c r="Z20">
-        <v>0</v>
-      </c>
-      <c r="AA20">
-        <v>0</v>
-      </c>
-      <c r="AB20">
-        <v>0.09626800013532681</v>
-      </c>
-      <c r="AC20">
-        <v>-0.09626800013532681</v>
-      </c>
-      <c r="AD20">
-        <v>1493.3</v>
-      </c>
-      <c r="AE20">
-        <v>0</v>
-      </c>
-      <c r="AF20">
-        <v>1493.3</v>
-      </c>
-      <c r="AG20">
-        <v>401.7</v>
-      </c>
-      <c r="AH20">
-        <v>0.771133488252001</v>
-      </c>
-      <c r="AI20">
-        <v>0.6940739019288868</v>
-      </c>
-      <c r="AJ20">
-        <v>0.4754408805775832</v>
-      </c>
-      <c r="AK20">
-        <v>0.3789980186810076</v>
-      </c>
-      <c r="AL20">
-        <v>0</v>
-      </c>
-      <c r="AM20">
+      <c r="K22">
+        <v>-373</v>
+      </c>
+      <c r="M22">
+        <v>-0</v>
+      </c>
+      <c r="N22">
+        <v>-0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>-0</v>
+      </c>
+      <c r="Q22">
+        <v>-0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>296</v>
+      </c>
+      <c r="V22">
+        <v>0.3062913907284768</v>
+      </c>
+      <c r="W22">
+        <v>-0.5400318517446069</v>
+      </c>
+      <c r="X22">
+        <v>0.102252445702849</v>
+      </c>
+      <c r="Y22">
+        <v>-0.6422842974474559</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0.07155571907985443</v>
+      </c>
+      <c r="AC22">
+        <v>-0.07155571907985443</v>
+      </c>
+      <c r="AD22">
+        <v>1465.5</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>1465.5</v>
+      </c>
+      <c r="AG22">
+        <v>1169.5</v>
+      </c>
+      <c r="AH22">
+        <v>0.6026152391134504</v>
+      </c>
+      <c r="AI22">
+        <v>0.5748185918807609</v>
+      </c>
+      <c r="AJ22">
+        <v>0.5475443606910436</v>
+      </c>
+      <c r="AK22">
+        <v>0.518970490348347</v>
+      </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>PT Bank Pembangunan Daerah Jawa Barat dan Banten Tbk (IDX:BJBR)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D23">
+        <v>0.0504</v>
+      </c>
+      <c r="E23">
+        <v>0.0518</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>123.2</v>
+      </c>
+      <c r="L23">
+        <v>0.21493370551291</v>
+      </c>
+      <c r="M23">
+        <v>71.20699999999999</v>
+      </c>
+      <c r="N23">
+        <v>0.09145517595684562</v>
+      </c>
+      <c r="O23">
+        <v>0.5779788961038961</v>
+      </c>
+      <c r="P23">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="Q23">
+        <v>0.09131774980734651</v>
+      </c>
+      <c r="R23">
+        <v>0.5771103896103895</v>
+      </c>
+      <c r="S23">
+        <v>0.1069999999999993</v>
+      </c>
+      <c r="T23">
+        <v>0.001502661255213663</v>
+      </c>
+      <c r="U23">
+        <v>277.2</v>
+      </c>
+      <c r="V23">
+        <v>0.3560236321602877</v>
+      </c>
+      <c r="W23">
+        <v>0.1343511450381679</v>
+      </c>
+      <c r="X23">
+        <v>0.1221069269297784</v>
+      </c>
+      <c r="Y23">
+        <v>0.01224421810838951</v>
+      </c>
+      <c r="Z23">
+        <v>0.2803893753363009</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>0.07218333617574271</v>
+      </c>
+      <c r="AC23">
+        <v>-0.07218333617574271</v>
+      </c>
+      <c r="AD23">
+        <v>1862.5</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>1862.5</v>
+      </c>
+      <c r="AG23">
+        <v>1585.3</v>
+      </c>
+      <c r="AH23">
+        <v>0.7051985914959676</v>
+      </c>
+      <c r="AI23">
+        <v>0.6574534928871474</v>
+      </c>
+      <c r="AJ23">
+        <v>0.670629045221879</v>
+      </c>
+      <c r="AK23">
+        <v>0.6202997221896154</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>PT Bank BTPN Tbk (IDX:BTPN)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D24">
+        <v>0.0546</v>
+      </c>
+      <c r="E24">
+        <v>0.134</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>-0.005364154729854922</v>
+      </c>
+      <c r="J24">
+        <v>-0.004191882784370425</v>
+      </c>
+      <c r="K24">
+        <v>179.1</v>
+      </c>
+      <c r="L24">
+        <v>0.2401448109412711</v>
+      </c>
+      <c r="M24">
+        <v>40</v>
+      </c>
+      <c r="N24">
+        <v>0.02915239414036878</v>
+      </c>
+      <c r="O24">
+        <v>0.2233389168062535</v>
+      </c>
+      <c r="P24">
+        <v>40</v>
+      </c>
+      <c r="Q24">
+        <v>0.02915239414036878</v>
+      </c>
+      <c r="R24">
+        <v>0.2233389168062535</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>896.6</v>
+      </c>
+      <c r="V24">
+        <v>0.6534509146563662</v>
+      </c>
+      <c r="W24">
+        <v>0.0752805682821235</v>
+      </c>
+      <c r="X24">
+        <v>0.1120950071225317</v>
+      </c>
+      <c r="Y24">
+        <v>-0.03681443884040822</v>
+      </c>
+      <c r="Z24">
+        <v>0.1483223367588072</v>
+      </c>
+      <c r="AA24">
+        <v>-0.0006217498499968366</v>
+      </c>
+      <c r="AB24">
+        <v>0.07191341336914181</v>
+      </c>
+      <c r="AC24">
+        <v>-0.07253516321913865</v>
+      </c>
+      <c r="AD24">
+        <v>2654.9</v>
+      </c>
+      <c r="AE24">
+        <v>21.447932987629</v>
+      </c>
+      <c r="AF24">
+        <v>2676.347932987629</v>
+      </c>
+      <c r="AG24">
+        <v>1779.747932987629</v>
+      </c>
+      <c r="AH24">
+        <v>0.6610799934414785</v>
+      </c>
+      <c r="AI24">
+        <v>0.5023130359652948</v>
+      </c>
+      <c r="AJ24">
+        <v>0.5646680838756742</v>
+      </c>
+      <c r="AK24">
+        <v>0.4016177014603317</v>
+      </c>
+      <c r="AL24">
+        <v>0</v>
+      </c>
+      <c r="AM24">
+        <v>0</v>
+      </c>
+      <c r="AN24">
+        <v>9186.50519031142</v>
+      </c>
+      <c r="AP24">
+        <v>6158.297345977956</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>PT Bank Nationalnobu Tbk (IDX:NOBU)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D25">
+        <v>0.108</v>
+      </c>
+      <c r="E25">
+        <v>0.22</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>8.58</v>
+      </c>
+      <c r="L25">
+        <v>0.1628083491461101</v>
+      </c>
+      <c r="M25">
+        <v>-0</v>
+      </c>
+      <c r="N25">
+        <v>-0</v>
+      </c>
+      <c r="O25">
+        <v>-0</v>
+      </c>
+      <c r="P25">
+        <v>-0</v>
+      </c>
+      <c r="Q25">
+        <v>-0</v>
+      </c>
+      <c r="R25">
+        <v>-0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>109.8</v>
+      </c>
+      <c r="V25">
+        <v>0.3083403538331929</v>
+      </c>
+      <c r="W25">
+        <v>0.07333333333333333</v>
+      </c>
+      <c r="X25">
+        <v>0.08767092878102943</v>
+      </c>
+      <c r="Y25">
+        <v>-0.0143375954476961</v>
+      </c>
+      <c r="Z25">
+        <v>0.2218013468013468</v>
+      </c>
+      <c r="AA25">
+        <v>0</v>
+      </c>
+      <c r="AB25">
+        <v>0.0728345346741886</v>
+      </c>
+      <c r="AC25">
+        <v>-0.0728345346741886</v>
+      </c>
+      <c r="AD25">
+        <v>311</v>
+      </c>
+      <c r="AE25">
+        <v>0</v>
+      </c>
+      <c r="AF25">
+        <v>311</v>
+      </c>
+      <c r="AG25">
+        <v>201.2</v>
+      </c>
+      <c r="AH25">
+        <v>0.4661969719682206</v>
+      </c>
+      <c r="AI25">
+        <v>0.5936247375453331</v>
+      </c>
+      <c r="AJ25">
+        <v>0.3610263771756684</v>
+      </c>
+      <c r="AK25">
+        <v>0.4858729775416565</v>
+      </c>
+      <c r="AL25">
+        <v>0</v>
+      </c>
+      <c r="AM25">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/indonesia/indonesia_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/indonesia/indonesia_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.115</v>
+        <v>0.133</v>
       </c>
       <c r="E2">
-        <v>0.1455</v>
+        <v>0.114</v>
       </c>
       <c r="F2">
-        <v>0.08044999999999999</v>
+        <v>0.106</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,91 +603,91 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>-3.161073515532116E-05</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>-2.565130192973307E-05</v>
       </c>
       <c r="K2">
-        <v>7872.200000000001</v>
+        <v>12751.63</v>
       </c>
       <c r="L2">
-        <v>0.4433543590898851</v>
+        <v>0.4115712588920304</v>
       </c>
       <c r="M2">
-        <v>5436.9</v>
+        <v>8191.9842</v>
       </c>
       <c r="N2">
-        <v>0.07647674428418308</v>
+        <v>0.04732799775376452</v>
       </c>
       <c r="O2">
-        <v>0.690645562866797</v>
+        <v>0.6424264348949899</v>
       </c>
       <c r="P2">
-        <v>5359.2</v>
+        <v>8107.5442</v>
       </c>
       <c r="Q2">
-        <v>0.07538379737861538</v>
+        <v>0.04684015792976585</v>
       </c>
       <c r="R2">
-        <v>0.6807753868041969</v>
+        <v>0.6358045363612338</v>
       </c>
       <c r="S2">
-        <v>77.69999999999982</v>
+        <v>84.43999999999981</v>
       </c>
       <c r="T2">
-        <v>0.0142912321359598</v>
+        <v>0.01030763706795233</v>
       </c>
       <c r="U2">
-        <v>9651.099999999999</v>
+        <v>17577.9</v>
       </c>
       <c r="V2">
-        <v>0.1357546960144713</v>
+        <v>0.1015537617511393</v>
       </c>
       <c r="W2">
-        <v>0.22376255417607</v>
+        <v>0.06065906934916953</v>
       </c>
       <c r="X2">
-        <v>0.08096352707382155</v>
+        <v>0.07768952452579296</v>
       </c>
       <c r="Y2">
-        <v>0.1427990271022485</v>
+        <v>-0.01703045517662343</v>
       </c>
       <c r="Z2">
-        <v>0.3627745428542241</v>
+        <v>0.3486233700984383</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07506940996585708</v>
+        <v>0.07384654987885109</v>
       </c>
       <c r="AC2">
-        <v>-0.07506940996585708</v>
+        <v>-0.07384654987885109</v>
       </c>
       <c r="AD2">
-        <v>26891.6</v>
+        <v>44306.789</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>4.896945425851422</v>
       </c>
       <c r="AF2">
-        <v>26891.6</v>
+        <v>44311.68594542585</v>
       </c>
       <c r="AG2">
-        <v>17240.5</v>
+        <v>26733.78594542585</v>
       </c>
       <c r="AH2">
-        <v>0.2744494498070089</v>
+        <v>0.203824396680659</v>
       </c>
       <c r="AI2">
-        <v>0.3922539915923485</v>
+        <v>0.3538218319800971</v>
       </c>
       <c r="AJ2">
-        <v>0.195176871079453</v>
+        <v>0.1337870731142909</v>
       </c>
       <c r="AK2">
-        <v>0.292680649514901</v>
+        <v>0.2483182094218669</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -704,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PT Bank Rakyat Indonesia (Persero) Tbk (IDX:BBRI)</t>
+          <t>PT Krom Bank Indonesia Tbk (IDX:BBSI)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,13 +713,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.11</v>
+        <v>0.459</v>
       </c>
       <c r="E3">
-        <v>0.127</v>
-      </c>
-      <c r="F3">
-        <v>0.0699</v>
+        <v>0.439</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,85 +731,82 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>4040.4</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="L3">
-        <v>0.4527160272499104</v>
+        <v>0.4091703056768559</v>
       </c>
       <c r="M3">
-        <v>3254.9</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.08541206354537868</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.8055885555885555</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>3177.2</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.08337313229173773</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.7863577863577863</v>
+        <v>-0</v>
       </c>
       <c r="S3">
-        <v>77.69999999999982</v>
-      </c>
-      <c r="T3">
-        <v>0.02387170112753075</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>4964.9</v>
+        <v>22.8</v>
       </c>
       <c r="V3">
-        <v>0.1302842957683648</v>
+        <v>0.02382694116417599</v>
       </c>
       <c r="W3">
-        <v>0.203877322407129</v>
+        <v>0.04586392559960841</v>
       </c>
       <c r="X3">
-        <v>0.07926911599160072</v>
+        <v>0.07285193209744684</v>
       </c>
       <c r="Y3">
-        <v>0.1246082064155282</v>
+        <v>-0.02698800649783843</v>
       </c>
       <c r="Z3">
-        <v>0.3467759796398112</v>
+        <v>0.1159728552618252</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.07473130796683387</v>
+        <v>0.07285193209744684</v>
       </c>
       <c r="AC3">
-        <v>-0.07473130796683387</v>
+        <v>-0.07285193209744684</v>
       </c>
       <c r="AD3">
-        <v>11576</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>11576</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>6611.1</v>
+        <v>-22.8</v>
       </c>
       <c r="AH3">
-        <v>0.2329915747863506</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.3472345122788915</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>0.1478354983195175</v>
+        <v>-0.02440852157156621</v>
       </c>
       <c r="AK3">
-        <v>0.2330083742175605</v>
+        <v>-0.1168032786885246</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -829,120 +823,2747 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>PT Bank Amar Indonesia Tbk (IDX:AMAR)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.24</v>
+      </c>
+      <c r="E4">
+        <v>0.22</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>11.1</v>
+      </c>
+      <c r="L4">
+        <v>0.2155339805825243</v>
+      </c>
+      <c r="M4">
+        <v>13.53</v>
+      </c>
+      <c r="N4">
+        <v>0.06343178621659634</v>
+      </c>
+      <c r="O4">
+        <v>1.218918918918919</v>
+      </c>
+      <c r="P4">
+        <v>6.79</v>
+      </c>
+      <c r="Q4">
+        <v>0.03183309892170651</v>
+      </c>
+      <c r="R4">
+        <v>0.6117117117117117</v>
+      </c>
+      <c r="S4">
+        <v>6.740000000000001</v>
+      </c>
+      <c r="T4">
+        <v>0.4981522542498152</v>
+      </c>
+      <c r="U4">
+        <v>41.3</v>
+      </c>
+      <c r="V4">
+        <v>0.193624003750586</v>
+      </c>
+      <c r="W4">
+        <v>0.05098759761139182</v>
+      </c>
+      <c r="X4">
+        <v>0.07285193209744684</v>
+      </c>
+      <c r="Y4">
+        <v>-0.02186433448605501</v>
+      </c>
+      <c r="Z4">
+        <v>0.3774995601946872</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0.07285193209744684</v>
+      </c>
+      <c r="AC4">
+        <v>-0.07285193209744684</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>-41.3</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.2401162790697674</v>
+      </c>
+      <c r="AK4">
+        <v>-0.258125</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PT Bank Central Asia Tbk (IDX:BBCA)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>0.0993</v>
+      </c>
+      <c r="E5">
+        <v>0.135</v>
+      </c>
+      <c r="F5">
+        <v>0.106</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>3520</v>
+      </c>
+      <c r="L5">
+        <v>0.509937996175465</v>
+      </c>
+      <c r="M5">
+        <v>2198.4</v>
+      </c>
+      <c r="N5">
+        <v>0.02972960180671161</v>
+      </c>
+      <c r="O5">
+        <v>0.6245454545454546</v>
+      </c>
+      <c r="P5">
+        <v>2198.4</v>
+      </c>
+      <c r="Q5">
+        <v>0.02972960180671161</v>
+      </c>
+      <c r="R5">
+        <v>0.6245454545454546</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>1498.5</v>
+      </c>
+      <c r="V5">
+        <v>0.0202646507948314</v>
+      </c>
+      <c r="W5">
+        <v>0.2309984118859183</v>
+      </c>
+      <c r="X5">
+        <v>0.07291525088212616</v>
+      </c>
+      <c r="Y5">
+        <v>0.1580831610037921</v>
+      </c>
+      <c r="Z5">
+        <v>0.5356488810255455</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0.07286198891619088</v>
+      </c>
+      <c r="AC5">
+        <v>-0.07286198891619088</v>
+      </c>
+      <c r="AD5">
+        <v>221.9</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>221.9</v>
+      </c>
+      <c r="AG5">
+        <v>-1276.6</v>
+      </c>
+      <c r="AH5">
+        <v>0.002991840190701161</v>
+      </c>
+      <c r="AI5">
+        <v>0.0129553190371378</v>
+      </c>
+      <c r="AJ5">
+        <v>-0.01756710825252271</v>
+      </c>
+      <c r="AK5">
+        <v>-0.08167835389261401</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PT Bank Maspion Indonesia Tbk (IDX:BMAS)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>0.165</v>
+      </c>
+      <c r="E6">
+        <v>-0.00245</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>4.32</v>
+      </c>
+      <c r="L6">
+        <v>0.1244956772334294</v>
+      </c>
+      <c r="M6">
+        <v>-0</v>
+      </c>
+      <c r="N6">
+        <v>-0</v>
+      </c>
+      <c r="O6">
+        <v>-0</v>
+      </c>
+      <c r="P6">
+        <v>-0</v>
+      </c>
+      <c r="Q6">
+        <v>-0</v>
+      </c>
+      <c r="R6">
+        <v>-0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>34.8</v>
+      </c>
+      <c r="V6">
+        <v>0.05300030459945172</v>
+      </c>
+      <c r="W6">
+        <v>0.02023419203747073</v>
+      </c>
+      <c r="X6">
+        <v>0.0729113837240332</v>
+      </c>
+      <c r="Y6">
+        <v>-0.05267719168656248</v>
+      </c>
+      <c r="Z6">
+        <v>0.2010347204922164</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0.07287452548971796</v>
+      </c>
+      <c r="AC6">
+        <v>-0.07287452548971796</v>
+      </c>
+      <c r="AD6">
+        <v>1.85</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>1.85</v>
+      </c>
+      <c r="AG6">
+        <v>-32.95</v>
+      </c>
+      <c r="AH6">
+        <v>0.00280962867339965</v>
+      </c>
+      <c r="AI6">
+        <v>0.004450860098640683</v>
+      </c>
+      <c r="AJ6">
+        <v>-0.05283412170287821</v>
+      </c>
+      <c r="AK6">
+        <v>-0.0865170014441381</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PT Bank Panin Dubai Syariah Tbk (IDX:PNBS)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>0.147</v>
+      </c>
+      <c r="E7">
+        <v>0.479</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>8.09</v>
+      </c>
+      <c r="L7">
+        <v>0.227887323943662</v>
+      </c>
+      <c r="M7">
+        <v>-0</v>
+      </c>
+      <c r="N7">
+        <v>-0</v>
+      </c>
+      <c r="O7">
+        <v>-0</v>
+      </c>
+      <c r="P7">
+        <v>-0</v>
+      </c>
+      <c r="Q7">
+        <v>-0</v>
+      </c>
+      <c r="R7">
+        <v>-0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="V7">
+        <v>0.5910224438902743</v>
+      </c>
+      <c r="W7">
+        <v>0.04580973952434881</v>
+      </c>
+      <c r="X7">
+        <v>0.07301663181570794</v>
+      </c>
+      <c r="Y7">
+        <v>-0.02720689229135913</v>
+      </c>
+      <c r="Z7">
+        <v>0.2733502733502733</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0.07287796637182216</v>
+      </c>
+      <c r="AC7">
+        <v>-0.07287796637182216</v>
+      </c>
+      <c r="AD7">
+        <v>0.9389999999999999</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0.9389999999999999</v>
+      </c>
+      <c r="AG7">
+        <v>-70.161</v>
+      </c>
+      <c r="AH7">
+        <v>0.00774503253903447</v>
+      </c>
+      <c r="AI7">
+        <v>0.004884544759388053</v>
+      </c>
+      <c r="AJ7">
+        <v>-1.399329862980913</v>
+      </c>
+      <c r="AK7">
+        <v>-0.5791776389106729</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>PT Bank Aladin Syariah Tbk (IDX:BANK)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>-10.6</v>
+      </c>
+      <c r="L8">
+        <v>-0.4308943089430894</v>
+      </c>
+      <c r="M8">
+        <v>-0</v>
+      </c>
+      <c r="N8">
+        <v>-0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>-0</v>
+      </c>
+      <c r="Q8">
+        <v>-0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>130.3</v>
+      </c>
+      <c r="V8">
+        <v>0.1742211525605028</v>
+      </c>
+      <c r="W8">
+        <v>-0.05326633165829146</v>
+      </c>
+      <c r="X8">
+        <v>0.07317920296469874</v>
+      </c>
+      <c r="Y8">
+        <v>-0.1264455346229902</v>
+      </c>
+      <c r="Z8">
+        <v>0.2673041399543627</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0.07294496754540139</v>
+      </c>
+      <c r="AC8">
+        <v>-0.07294496754540139</v>
+      </c>
+      <c r="AD8">
+        <v>11.6</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>11.6</v>
+      </c>
+      <c r="AG8">
+        <v>-118.7</v>
+      </c>
+      <c r="AH8">
+        <v>0.01527320605661619</v>
+      </c>
+      <c r="AI8">
+        <v>0.05353022611905861</v>
+      </c>
+      <c r="AJ8">
+        <v>-0.1886522568340751</v>
+      </c>
+      <c r="AK8">
+        <v>-1.373842592592593</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>PT Bank Mestika Dharma Tbk (IDX:BBMD)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>0.0788</v>
+      </c>
+      <c r="E9">
+        <v>0.101</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>28.3</v>
+      </c>
+      <c r="L9">
+        <v>0.4071942446043166</v>
+      </c>
+      <c r="M9">
+        <v>8.0542</v>
+      </c>
+      <c r="N9">
+        <v>0.01671342602199627</v>
+      </c>
+      <c r="O9">
+        <v>0.2846007067137809</v>
+      </c>
+      <c r="P9">
+        <v>8.0542</v>
+      </c>
+      <c r="Q9">
+        <v>0.01671342602199627</v>
+      </c>
+      <c r="R9">
+        <v>0.2846007067137809</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>12.8</v>
+      </c>
+      <c r="V9">
+        <v>0.02656152728781905</v>
+      </c>
+      <c r="W9">
+        <v>0.09197270068248295</v>
+      </c>
+      <c r="X9">
+        <v>0.07347369428858881</v>
+      </c>
+      <c r="Y9">
+        <v>0.01849900639389414</v>
+      </c>
+      <c r="Z9">
+        <v>0.2409012131715772</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0.07294814677931802</v>
+      </c>
+      <c r="AC9">
+        <v>-0.07294814677931802</v>
+      </c>
+      <c r="AD9">
+        <v>14.2</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>14.2</v>
+      </c>
+      <c r="AG9">
+        <v>1.399999999999999</v>
+      </c>
+      <c r="AH9">
+        <v>0.02862326143922596</v>
+      </c>
+      <c r="AI9">
+        <v>0.0407694516221648</v>
+      </c>
+      <c r="AJ9">
+        <v>0.002896751500103453</v>
+      </c>
+      <c r="AK9">
+        <v>0.004172876304023841</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>PT Bank Jago Tbk (IDX:ARTO)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>1.709</v>
+      </c>
+      <c r="F10">
+        <v>1.396</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>7.13</v>
+      </c>
+      <c r="L10">
+        <v>0.07275510204081632</v>
+      </c>
+      <c r="M10">
+        <v>-0</v>
+      </c>
+      <c r="N10">
+        <v>-0</v>
+      </c>
+      <c r="O10">
+        <v>-0</v>
+      </c>
+      <c r="P10">
+        <v>-0</v>
+      </c>
+      <c r="Q10">
+        <v>-0</v>
+      </c>
+      <c r="R10">
+        <v>-0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>151.9</v>
+      </c>
+      <c r="V10">
+        <v>0.07348459194039959</v>
+      </c>
+      <c r="W10">
+        <v>0.01323556710599592</v>
+      </c>
+      <c r="X10">
+        <v>0.07322247459921602</v>
+      </c>
+      <c r="Y10">
+        <v>-0.0599869074932201</v>
+      </c>
+      <c r="Z10">
+        <v>0.2043667758013054</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0.07299070902613002</v>
+      </c>
+      <c r="AC10">
+        <v>-0.07299070902613002</v>
+      </c>
+      <c r="AD10">
+        <v>36.3</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>36.3</v>
+      </c>
+      <c r="AG10">
+        <v>-115.6</v>
+      </c>
+      <c r="AH10">
+        <v>0.01725777312921936</v>
+      </c>
+      <c r="AI10">
+        <v>0.0609469442578912</v>
+      </c>
+      <c r="AJ10">
+        <v>-0.05923648475531643</v>
+      </c>
+      <c r="AK10">
+        <v>-0.260536398467433</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>PT Bank Ina Perdana Tbk (IDX:BINA)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>0.336</v>
+      </c>
+      <c r="E11">
+        <v>0.6579999999999999</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>9.75</v>
+      </c>
+      <c r="L11">
+        <v>0.2332535885167464</v>
+      </c>
+      <c r="M11">
+        <v>-0</v>
+      </c>
+      <c r="N11">
+        <v>-0</v>
+      </c>
+      <c r="O11">
+        <v>-0</v>
+      </c>
+      <c r="P11">
+        <v>-0</v>
+      </c>
+      <c r="Q11">
+        <v>-0</v>
+      </c>
+      <c r="R11">
+        <v>-0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>150.3</v>
+      </c>
+      <c r="V11">
+        <v>0.09430884106168037</v>
+      </c>
+      <c r="W11">
+        <v>0.04304635761589404</v>
+      </c>
+      <c r="X11">
+        <v>0.07397467978939232</v>
+      </c>
+      <c r="Y11">
+        <v>-0.03092832217349828</v>
+      </c>
+      <c r="Z11">
+        <v>0.5708043151713776</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0.07325819486524966</v>
+      </c>
+      <c r="AC11">
+        <v>-0.07325819486524966</v>
+      </c>
+      <c r="AD11">
+        <v>84.8</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>84.8</v>
+      </c>
+      <c r="AG11">
+        <v>-65.50000000000001</v>
+      </c>
+      <c r="AH11">
+        <v>0.05052129877867143</v>
+      </c>
+      <c r="AI11">
+        <v>0.2591687041564792</v>
+      </c>
+      <c r="AJ11">
+        <v>-0.04286088208349693</v>
+      </c>
+      <c r="AK11">
+        <v>-0.3702656868287169</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>PT Bank Syariah Indonesia Tbk (IDX:BRIS)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>0.701</v>
+      </c>
+      <c r="E12">
+        <v>2.098</v>
+      </c>
+      <c r="F12">
+        <v>0.17</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>383.9</v>
+      </c>
+      <c r="L12">
+        <v>0.3279514778745942</v>
+      </c>
+      <c r="M12">
+        <v>52.3</v>
+      </c>
+      <c r="N12">
+        <v>0.006698429775352852</v>
+      </c>
+      <c r="O12">
+        <v>0.1362333941130503</v>
+      </c>
+      <c r="P12">
+        <v>52.3</v>
+      </c>
+      <c r="Q12">
+        <v>0.006698429775352852</v>
+      </c>
+      <c r="R12">
+        <v>0.1362333941130503</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>1732.2</v>
+      </c>
+      <c r="V12">
+        <v>0.2218550680089142</v>
+      </c>
+      <c r="W12">
+        <v>0.1605335786568537</v>
+      </c>
+      <c r="X12">
+        <v>0.07486636867940856</v>
+      </c>
+      <c r="Y12">
+        <v>0.08566720997744516</v>
+      </c>
+      <c r="Z12">
+        <v>0.395152578990008</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0.07338279087561531</v>
+      </c>
+      <c r="AC12">
+        <v>-0.07338279087561531</v>
+      </c>
+      <c r="AD12">
+        <v>745.4</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>745.4</v>
+      </c>
+      <c r="AG12">
+        <v>-986.8000000000001</v>
+      </c>
+      <c r="AH12">
+        <v>0.08714866950381144</v>
+      </c>
+      <c r="AI12">
+        <v>0.2262696172176183</v>
+      </c>
+      <c r="AJ12">
+        <v>-0.1446708693739921</v>
+      </c>
+      <c r="AK12">
+        <v>-0.6317137187119903</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>PT Allo Bank Indonesia Tbk (IDX:BBHI)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D13">
+        <v>1.693</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>27</v>
+      </c>
+      <c r="L13">
+        <v>0.3366583541147132</v>
+      </c>
+      <c r="M13">
+        <v>-0</v>
+      </c>
+      <c r="N13">
+        <v>-0</v>
+      </c>
+      <c r="O13">
+        <v>-0</v>
+      </c>
+      <c r="P13">
+        <v>-0</v>
+      </c>
+      <c r="Q13">
+        <v>-0</v>
+      </c>
+      <c r="R13">
+        <v>-0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>51.5</v>
+      </c>
+      <c r="V13">
+        <v>0.05460714664404623</v>
+      </c>
+      <c r="W13">
+        <v>0.06129398410896708</v>
+      </c>
+      <c r="X13">
+        <v>0.07515417170512922</v>
+      </c>
+      <c r="Y13">
+        <v>-0.01386018759616214</v>
+      </c>
+      <c r="Z13">
+        <v>0.2130598799213644</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0.07345117366615196</v>
+      </c>
+      <c r="AC13">
+        <v>-0.07345117366615196</v>
+      </c>
+      <c r="AD13">
+        <v>102.9</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>102.9</v>
+      </c>
+      <c r="AG13">
+        <v>51.40000000000001</v>
+      </c>
+      <c r="AH13">
+        <v>0.09837476099426387</v>
+      </c>
+      <c r="AI13">
+        <v>0.1774749913763367</v>
+      </c>
+      <c r="AJ13">
+        <v>0.05168426344896934</v>
+      </c>
+      <c r="AK13">
+        <v>0.09729320461858794</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>PT Bank JTrust Indonesia Tbk (IDX:BCIC)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D14">
+        <v>0.176</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>5.14</v>
+      </c>
+      <c r="L14">
+        <v>0.06974219810040705</v>
+      </c>
+      <c r="M14">
+        <v>-0</v>
+      </c>
+      <c r="N14">
+        <v>-0</v>
+      </c>
+      <c r="O14">
+        <v>-0</v>
+      </c>
+      <c r="P14">
+        <v>-0</v>
+      </c>
+      <c r="Q14">
+        <v>-0</v>
+      </c>
+      <c r="R14">
+        <v>-0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>158.4</v>
+      </c>
+      <c r="V14">
+        <v>0.7542857142857143</v>
+      </c>
+      <c r="W14">
+        <v>0.02085192697768763</v>
+      </c>
+      <c r="X14">
+        <v>0.07611748675778149</v>
+      </c>
+      <c r="Y14">
+        <v>-0.05526555978009386</v>
+      </c>
+      <c r="Z14">
+        <v>0.3614144693288087</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0.07366830740439609</v>
+      </c>
+      <c r="AC14">
+        <v>-0.07366830740439609</v>
+      </c>
+      <c r="AD14">
+        <v>32.5</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>32.5</v>
+      </c>
+      <c r="AG14">
+        <v>-125.9</v>
+      </c>
+      <c r="AH14">
+        <v>0.134020618556701</v>
+      </c>
+      <c r="AI14">
+        <v>0.1107702794819359</v>
+      </c>
+      <c r="AJ14">
+        <v>-1.497027348394768</v>
+      </c>
+      <c r="AK14">
+        <v>-0.9325925925925929</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>PT Bank Pembangunan Daerah Jawa Timur Tbk (IDX:BJTM)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D15">
+        <v>0.05309999999999999</v>
+      </c>
+      <c r="E15">
+        <v>-0.00536</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>86.2</v>
+      </c>
+      <c r="L15">
+        <v>0.2484865955606803</v>
+      </c>
+      <c r="M15">
+        <v>53.9</v>
+      </c>
+      <c r="N15">
+        <v>0.1072210065645514</v>
+      </c>
+      <c r="O15">
+        <v>0.6252900232018561</v>
+      </c>
+      <c r="P15">
+        <v>53.9</v>
+      </c>
+      <c r="Q15">
+        <v>0.1072210065645514</v>
+      </c>
+      <c r="R15">
+        <v>0.6252900232018561</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>404.3</v>
+      </c>
+      <c r="V15">
+        <v>0.8042570121344739</v>
+      </c>
+      <c r="W15">
+        <v>0.1125767271777458</v>
+      </c>
+      <c r="X15">
+        <v>0.08415982267930618</v>
+      </c>
+      <c r="Y15">
+        <v>0.02841690449843967</v>
+      </c>
+      <c r="Z15">
+        <v>0.7185169842584922</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0.0740247923533061</v>
+      </c>
+      <c r="AC15">
+        <v>-0.0740247923533061</v>
+      </c>
+      <c r="AD15">
+        <v>269.4</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>269.4</v>
+      </c>
+      <c r="AG15">
+        <v>-134.9</v>
+      </c>
+      <c r="AH15">
+        <v>0.3489185338686699</v>
+      </c>
+      <c r="AI15">
+        <v>0.2483178173103511</v>
+      </c>
+      <c r="AJ15">
+        <v>-0.3667754214246874</v>
+      </c>
+      <c r="AK15">
+        <v>-0.198207464002351</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PT Bank Pan Indonesia Tbk (IDX:PNBN)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D16">
+        <v>-0.021</v>
+      </c>
+      <c r="E16">
+        <v>-0.07429999999999999</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>152.2</v>
+      </c>
+      <c r="L16">
+        <v>0.2571380300726474</v>
+      </c>
+      <c r="M16">
+        <v>-0</v>
+      </c>
+      <c r="N16">
+        <v>-0</v>
+      </c>
+      <c r="O16">
+        <v>-0</v>
+      </c>
+      <c r="P16">
+        <v>-0</v>
+      </c>
+      <c r="Q16">
+        <v>-0</v>
+      </c>
+      <c r="R16">
+        <v>-0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>504.9</v>
+      </c>
+      <c r="V16">
+        <v>0.1818083612401426</v>
+      </c>
+      <c r="W16">
+        <v>0.04721136546932191</v>
+      </c>
+      <c r="X16">
+        <v>0.08059813026215487</v>
+      </c>
+      <c r="Y16">
+        <v>-0.03338676479283296</v>
+      </c>
+      <c r="Z16">
+        <v>0.183075067272896</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0.07448765836806084</v>
+      </c>
+      <c r="AC16">
+        <v>-0.07448765836806084</v>
+      </c>
+      <c r="AD16">
+        <v>1019.5</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>1019.5</v>
+      </c>
+      <c r="AG16">
+        <v>514.6</v>
+      </c>
+      <c r="AH16">
+        <v>0.2685297371332245</v>
+      </c>
+      <c r="AI16">
+        <v>0.2164313767116017</v>
+      </c>
+      <c r="AJ16">
+        <v>0.1563325941003129</v>
+      </c>
+      <c r="AK16">
+        <v>0.1223606619745102</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PT Bank Capital Indonesia Tbk (IDX:BACA)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D17">
+        <v>0.146</v>
+      </c>
+      <c r="E17">
+        <v>0.0859</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>8.73</v>
+      </c>
+      <c r="L17">
+        <v>0.1489761092150171</v>
+      </c>
+      <c r="M17">
+        <v>-0</v>
+      </c>
+      <c r="N17">
+        <v>-0</v>
+      </c>
+      <c r="O17">
+        <v>-0</v>
+      </c>
+      <c r="P17">
+        <v>-0</v>
+      </c>
+      <c r="Q17">
+        <v>-0</v>
+      </c>
+      <c r="R17">
+        <v>-0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>41.6</v>
+      </c>
+      <c r="V17">
+        <v>0.256631708821715</v>
+      </c>
+      <c r="W17">
+        <v>0.04017487344684768</v>
+      </c>
+      <c r="X17">
+        <v>0.09934146437275673</v>
+      </c>
+      <c r="Y17">
+        <v>-0.05916659092590906</v>
+      </c>
+      <c r="Z17">
+        <v>0.2517182130584193</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0.07472296083240824</v>
+      </c>
+      <c r="AC17">
+        <v>-0.07472296083240824</v>
+      </c>
+      <c r="AD17">
+        <v>203.5</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>203.5</v>
+      </c>
+      <c r="AG17">
+        <v>161.9</v>
+      </c>
+      <c r="AH17">
+        <v>0.5566192560175054</v>
+      </c>
+      <c r="AI17">
+        <v>0.3674611773203323</v>
+      </c>
+      <c r="AJ17">
+        <v>0.4996913580246914</v>
+      </c>
+      <c r="AK17">
+        <v>0.3160874658336587</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PT Bank Rakyat Indonesia (Persero) Tbk (IDX:BBRI)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D18">
+        <v>0.11</v>
+      </c>
+      <c r="E18">
+        <v>0.127</v>
+      </c>
+      <c r="F18">
+        <v>0.0699</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>4040.4</v>
+      </c>
+      <c r="L18">
+        <v>0.4527160272499104</v>
+      </c>
+      <c r="M18">
+        <v>3254.9</v>
+      </c>
+      <c r="N18">
+        <v>0.08541206354537868</v>
+      </c>
+      <c r="O18">
+        <v>0.8055885555885555</v>
+      </c>
+      <c r="P18">
+        <v>3177.2</v>
+      </c>
+      <c r="Q18">
+        <v>0.08337313229173773</v>
+      </c>
+      <c r="R18">
+        <v>0.7863577863577863</v>
+      </c>
+      <c r="S18">
+        <v>77.69999999999982</v>
+      </c>
+      <c r="T18">
+        <v>0.02387170112753075</v>
+      </c>
+      <c r="U18">
+        <v>4964.9</v>
+      </c>
+      <c r="V18">
+        <v>0.1302842957683648</v>
+      </c>
+      <c r="W18">
+        <v>0.203877322407129</v>
+      </c>
+      <c r="X18">
+        <v>0.07926156229380443</v>
+      </c>
+      <c r="Y18">
+        <v>0.1246157601133245</v>
+      </c>
+      <c r="Z18">
+        <v>0.3467759796398112</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>0.07472551421698261</v>
+      </c>
+      <c r="AC18">
+        <v>-0.07472551421698261</v>
+      </c>
+      <c r="AD18">
+        <v>11576</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>11576</v>
+      </c>
+      <c r="AG18">
+        <v>6611.1</v>
+      </c>
+      <c r="AH18">
+        <v>0.2329915747863506</v>
+      </c>
+      <c r="AI18">
+        <v>0.3472345122788915</v>
+      </c>
+      <c r="AJ18">
+        <v>0.1478354983195175</v>
+      </c>
+      <c r="AK18">
+        <v>0.2330083742175605</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>PT Bank OCBC NISP Tbk (IDX:NISP)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D19">
+        <v>0.101</v>
+      </c>
+      <c r="E19">
+        <v>0.114</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>320.7</v>
+      </c>
+      <c r="L19">
+        <v>0.4038534189648659</v>
+      </c>
+      <c r="M19">
+        <v>109.1</v>
+      </c>
+      <c r="N19">
+        <v>0.05832041481798257</v>
+      </c>
+      <c r="O19">
+        <v>0.3401933270969754</v>
+      </c>
+      <c r="P19">
+        <v>109.1</v>
+      </c>
+      <c r="Q19">
+        <v>0.05832041481798257</v>
+      </c>
+      <c r="R19">
+        <v>0.3401933270969754</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>444.9</v>
+      </c>
+      <c r="V19">
+        <v>0.2378254129470252</v>
+      </c>
+      <c r="W19">
+        <v>0.1378998968008256</v>
+      </c>
+      <c r="X19">
+        <v>0.100323084546369</v>
+      </c>
+      <c r="Y19">
+        <v>0.03757681225445657</v>
+      </c>
+      <c r="Z19">
+        <v>0.2442482775590551</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0.07475308115314226</v>
+      </c>
+      <c r="AC19">
+        <v>-0.07475308115314226</v>
+      </c>
+      <c r="AD19">
+        <v>2435.5</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>2435.5</v>
+      </c>
+      <c r="AG19">
+        <v>1990.6</v>
+      </c>
+      <c r="AH19">
+        <v>0.5655798615949097</v>
+      </c>
+      <c r="AI19">
+        <v>0.480119068740513</v>
+      </c>
+      <c r="AJ19">
+        <v>0.5155258591666019</v>
+      </c>
+      <c r="AK19">
+        <v>0.430139591166429</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>PT Bank Tabungan Negara (Persero) Tbk (IDX:BBTN)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D20">
+        <v>0.0776</v>
+      </c>
+      <c r="E20">
+        <v>0.08119999999999999</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>216</v>
+      </c>
+      <c r="L20">
+        <v>0.2288620470438652</v>
+      </c>
+      <c r="M20">
+        <v>46.2</v>
+      </c>
+      <c r="N20">
+        <v>0.04657258064516129</v>
+      </c>
+      <c r="O20">
+        <v>0.2138888888888889</v>
+      </c>
+      <c r="P20">
+        <v>46.2</v>
+      </c>
+      <c r="Q20">
+        <v>0.04657258064516129</v>
+      </c>
+      <c r="R20">
+        <v>0.2138888888888889</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>234.5</v>
+      </c>
+      <c r="V20">
+        <v>0.2363911290322581</v>
+      </c>
+      <c r="W20">
+        <v>0.1150159744408946</v>
+      </c>
+      <c r="X20">
+        <v>0.1362832043072059</v>
+      </c>
+      <c r="Y20">
+        <v>-0.02126722986631135</v>
+      </c>
+      <c r="Z20">
+        <v>0.2944498174897826</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>0.07537428380314069</v>
+      </c>
+      <c r="AC20">
+        <v>-0.07537428380314069</v>
+      </c>
+      <c r="AD20">
+        <v>2982.1</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>2982.1</v>
+      </c>
+      <c r="AG20">
+        <v>2747.6</v>
+      </c>
+      <c r="AH20">
+        <v>0.7503837346820664</v>
+      </c>
+      <c r="AI20">
+        <v>0.5851614928770457</v>
+      </c>
+      <c r="AJ20">
+        <v>0.7347309872713659</v>
+      </c>
+      <c r="AK20">
+        <v>0.5651521072875743</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>PT Bank Mandiri (Persero) Tbk (IDX:BMRI)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D4">
+      <c r="D21">
         <v>0.12</v>
       </c>
-      <c r="E4">
+      <c r="E21">
         <v>0.164</v>
       </c>
-      <c r="F4">
+      <c r="F21">
         <v>0.091</v>
       </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
         <v>3831.8</v>
       </c>
-      <c r="L4">
+      <c r="L21">
         <v>0.4338934686112872</v>
       </c>
-      <c r="M4">
+      <c r="M21">
         <v>2182</v>
       </c>
-      <c r="N4">
+      <c r="N21">
         <v>0.06615328644191124</v>
       </c>
-      <c r="O4">
+      <c r="O21">
         <v>0.5694451693720967</v>
       </c>
-      <c r="P4">
+      <c r="P21">
         <v>2182</v>
       </c>
-      <c r="Q4">
+      <c r="Q21">
         <v>0.06615328644191124</v>
       </c>
-      <c r="R4">
+      <c r="R21">
         <v>0.5694451693720967</v>
       </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
         <v>4686.2</v>
       </c>
-      <c r="V4">
+      <c r="V21">
         <v>0.1420749454280864</v>
       </c>
-      <c r="W4">
+      <c r="W21">
         <v>0.2436477859450111</v>
       </c>
-      <c r="X4">
-        <v>0.08265793815604239</v>
-      </c>
-      <c r="Y4">
-        <v>0.1609898477889687</v>
-      </c>
-      <c r="Z4">
+      <c r="X21">
+        <v>0.08264961962960461</v>
+      </c>
+      <c r="Y21">
+        <v>0.1609981663154065</v>
+      </c>
+      <c r="Z21">
         <v>0.380515759312321</v>
       </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0.07540751196488028</v>
-      </c>
-      <c r="AC4">
-        <v>-0.07540751196488028</v>
-      </c>
-      <c r="AD4">
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0.07540183120818615</v>
+      </c>
+      <c r="AC21">
+        <v>-0.07540183120818615</v>
+      </c>
+      <c r="AD21">
         <v>15315.6</v>
       </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
         <v>15315.6</v>
       </c>
-      <c r="AG4">
+      <c r="AG21">
         <v>10629.4</v>
       </c>
-      <c r="AH4">
+      <c r="AH21">
         <v>0.3170957937539856</v>
       </c>
-      <c r="AI4">
+      <c r="AI21">
         <v>0.4348687778437146</v>
       </c>
-      <c r="AJ4">
+      <c r="AJ21">
         <v>0.2437186736186585</v>
       </c>
-      <c r="AK4">
+      <c r="AK21">
         <v>0.3481316752203376</v>
       </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>PT Bank Mega Tbk (IDX:MEGA)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D22">
+        <v>0.0421</v>
+      </c>
+      <c r="E22">
+        <v>0.0795</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>179.2</v>
+      </c>
+      <c r="L22">
+        <v>0.3968992248062015</v>
+      </c>
+      <c r="M22">
+        <v>162.3</v>
+      </c>
+      <c r="N22">
+        <v>0.05398483235763704</v>
+      </c>
+      <c r="O22">
+        <v>0.9056919642857144</v>
+      </c>
+      <c r="P22">
+        <v>162.3</v>
+      </c>
+      <c r="Q22">
+        <v>0.05398483235763704</v>
+      </c>
+      <c r="R22">
+        <v>0.9056919642857144</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>333.7</v>
+      </c>
+      <c r="V22">
+        <v>0.1109965407131453</v>
+      </c>
+      <c r="W22">
+        <v>0.1339112240322821</v>
+      </c>
+      <c r="X22">
+        <v>0.08303090540583</v>
+      </c>
+      <c r="Y22">
+        <v>0.05088031862645215</v>
+      </c>
+      <c r="Z22">
+        <v>0.2185488164964422</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0.07546877084919386</v>
+      </c>
+      <c r="AC22">
+        <v>-0.07546877084919386</v>
+      </c>
+      <c r="AD22">
+        <v>1450.3</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>1450.3</v>
+      </c>
+      <c r="AG22">
+        <v>1116.6</v>
+      </c>
+      <c r="AH22">
+        <v>0.3254201539255503</v>
+      </c>
+      <c r="AI22">
+        <v>0.5051725939600823</v>
+      </c>
+      <c r="AJ22">
+        <v>0.2708222168324036</v>
+      </c>
+      <c r="AK22">
+        <v>0.4400914393819959</v>
+      </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>PT Bank Pembangunan Daerah Jawa Barat dan Banten Tbk (IDX:BJBR)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D23">
+        <v>0.039</v>
+      </c>
+      <c r="E23">
+        <v>0.0238</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>99.5</v>
+      </c>
+      <c r="L23">
+        <v>0.1889838556505223</v>
+      </c>
+      <c r="M23">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="N23">
+        <v>0.1113544474393531</v>
+      </c>
+      <c r="O23">
+        <v>0.6643216080402009</v>
+      </c>
+      <c r="P23">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="Q23">
+        <v>0.1113544474393531</v>
+      </c>
+      <c r="R23">
+        <v>0.6643216080402009</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>942.5</v>
+      </c>
+      <c r="V23">
+        <v>1.587769541778976</v>
+      </c>
+      <c r="W23">
+        <v>0.1023241464417935</v>
+      </c>
+      <c r="X23">
+        <v>0.1550074103009894</v>
+      </c>
+      <c r="Y23">
+        <v>-0.05268326385919593</v>
+      </c>
+      <c r="Z23">
+        <v>0.2058490049653986</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>0.07552643777277057</v>
+      </c>
+      <c r="AC23">
+        <v>-0.07552643777277057</v>
+      </c>
+      <c r="AD23">
+        <v>2311.2</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>2311.2</v>
+      </c>
+      <c r="AG23">
+        <v>1368.7</v>
+      </c>
+      <c r="AH23">
+        <v>0.7956485816579455</v>
+      </c>
+      <c r="AI23">
+        <v>0.670982726085063</v>
+      </c>
+      <c r="AJ23">
+        <v>0.6974978341741833</v>
+      </c>
+      <c r="AK23">
+        <v>0.5470423661071142</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>PT Bank Nationalnobu Tbk (IDX:NOBU)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D24">
+        <v>0.169</v>
+      </c>
+      <c r="E24">
+        <v>0.4429999999999999</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>17.4</v>
+      </c>
+      <c r="L24">
+        <v>0.2478632478632478</v>
+      </c>
+      <c r="M24">
+        <v>-0</v>
+      </c>
+      <c r="N24">
+        <v>-0</v>
+      </c>
+      <c r="O24">
+        <v>-0</v>
+      </c>
+      <c r="P24">
+        <v>-0</v>
+      </c>
+      <c r="Q24">
+        <v>-0</v>
+      </c>
+      <c r="R24">
+        <v>-0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="V24">
+        <v>0.3672168042010502</v>
+      </c>
+      <c r="W24">
+        <v>0.08172851103804603</v>
+      </c>
+      <c r="X24">
+        <v>0.1005928462614415</v>
+      </c>
+      <c r="Y24">
+        <v>-0.01886433522339551</v>
+      </c>
+      <c r="Z24">
+        <v>0.1695242695001208</v>
+      </c>
+      <c r="AA24">
+        <v>0</v>
+      </c>
+      <c r="AB24">
+        <v>0.07631172989524969</v>
+      </c>
+      <c r="AC24">
+        <v>-0.07631172989524969</v>
+      </c>
+      <c r="AD24">
+        <v>350.5</v>
+      </c>
+      <c r="AE24">
+        <v>0</v>
+      </c>
+      <c r="AF24">
+        <v>350.5</v>
+      </c>
+      <c r="AG24">
+        <v>252.6</v>
+      </c>
+      <c r="AH24">
+        <v>0.56797925781883</v>
+      </c>
+      <c r="AI24">
+        <v>0.597307430129516</v>
+      </c>
+      <c r="AJ24">
+        <v>0.486517719568567</v>
+      </c>
+      <c r="AK24">
+        <v>0.5166700756800982</v>
+      </c>
+      <c r="AL24">
+        <v>0</v>
+      </c>
+      <c r="AM24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>PT Bank KB Bukopin Tbk (IDX:BBKP)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="K25">
+        <v>-353.1</v>
+      </c>
+      <c r="M25">
+        <v>-0</v>
+      </c>
+      <c r="N25">
+        <v>-0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>-0</v>
+      </c>
+      <c r="Q25">
+        <v>-0</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>184.1</v>
+      </c>
+      <c r="V25">
+        <v>0.2926868044515104</v>
+      </c>
+      <c r="W25">
+        <v>-0.3256779192030991</v>
+      </c>
+      <c r="X25">
+        <v>0.1246236530969253</v>
+      </c>
+      <c r="Y25">
+        <v>-0.4503015723000244</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+      <c r="AA25">
+        <v>0</v>
+      </c>
+      <c r="AB25">
+        <v>0.07717954887682044</v>
+      </c>
+      <c r="AC25">
+        <v>-0.07717954887682044</v>
+      </c>
+      <c r="AD25">
+        <v>1543.3</v>
+      </c>
+      <c r="AE25">
+        <v>0</v>
+      </c>
+      <c r="AF25">
+        <v>1543.3</v>
+      </c>
+      <c r="AG25">
+        <v>1359.2</v>
+      </c>
+      <c r="AH25">
+        <v>0.7104451503015237</v>
+      </c>
+      <c r="AI25">
+        <v>0.6709999999999999</v>
+      </c>
+      <c r="AJ25">
+        <v>0.6836334372799517</v>
+      </c>
+      <c r="AK25">
+        <v>0.6423744033271894</v>
+      </c>
+      <c r="AL25">
+        <v>0</v>
+      </c>
+      <c r="AM25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>PT Bank SMBC Indonesia Tbk (IDX:BTPN)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D26">
+        <v>0.0423</v>
+      </c>
+      <c r="E26">
+        <v>0.00864</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>-0.001169419803188399</v>
+      </c>
+      <c r="J26">
+        <v>-0.0009093118433178712</v>
+      </c>
+      <c r="K26">
+        <v>149.1</v>
+      </c>
+      <c r="L26">
+        <v>0.1780298507462686</v>
+      </c>
+      <c r="M26">
+        <v>45.2</v>
+      </c>
+      <c r="N26">
+        <v>0.03112733282831761</v>
+      </c>
+      <c r="O26">
+        <v>0.3031522468142187</v>
+      </c>
+      <c r="P26">
+        <v>45.2</v>
+      </c>
+      <c r="Q26">
+        <v>0.03112733282831761</v>
+      </c>
+      <c r="R26">
+        <v>0.3031522468142187</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>682.5</v>
+      </c>
+      <c r="V26">
+        <v>0.4700089525514772</v>
+      </c>
+      <c r="W26">
+        <v>0.06002415458937198</v>
+      </c>
+      <c r="X26">
+        <v>0.1251984661470673</v>
+      </c>
+      <c r="Y26">
+        <v>-0.06517431155769528</v>
+      </c>
+      <c r="Z26">
+        <v>0.1973724392597068</v>
+      </c>
+      <c r="AA26">
+        <v>-0.0001794730965633885</v>
+      </c>
+      <c r="AB26">
+        <v>0.07858313974365712</v>
+      </c>
+      <c r="AC26">
+        <v>-0.0787626128402205</v>
+      </c>
+      <c r="AD26">
+        <v>3597.5</v>
+      </c>
+      <c r="AE26">
+        <v>4.896945425851422</v>
+      </c>
+      <c r="AF26">
+        <v>3602.396945425851</v>
+      </c>
+      <c r="AG26">
+        <v>2919.896945425851</v>
+      </c>
+      <c r="AH26">
+        <v>0.7127112716302852</v>
+      </c>
+      <c r="AI26">
+        <v>0.5038460494644562</v>
+      </c>
+      <c r="AJ26">
+        <v>0.6678634458975909</v>
+      </c>
+      <c r="AK26">
+        <v>0.4514864509957313</v>
+      </c>
+      <c r="AL26">
+        <v>0</v>
+      </c>
+      <c r="AM26">
         <v>0</v>
       </c>
     </row>
